--- a/inst/extdata/medicaton_costs_all.xlsx
+++ b/inst/extdata/medicaton_costs_all.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sheej\Documents\Sheeja_WinLap\repos\packDAMipd\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DE195C-9855-4160-8C3A-225F08D957B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D31BC17C-1180-49AB-B822-8CF32AF217B0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$407</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="234">
   <si>
     <t>Drug</t>
   </si>
@@ -480,24 +484,15 @@
     <t>Panadol Ultra</t>
   </si>
   <si>
-    <t>12.8mg/500mg mg/mg</t>
-  </si>
-  <si>
     <t>Solpadeine Max</t>
   </si>
   <si>
-    <t>15mg/500mg mg/mg</t>
-  </si>
-  <si>
     <t>Codipar</t>
   </si>
   <si>
     <t>Efferevescent tablet</t>
   </si>
   <si>
-    <t>30mg/500mg mg/mg</t>
-  </si>
-  <si>
     <t>Kapake</t>
   </si>
   <si>
@@ -507,12 +502,6 @@
     <t>Zapain</t>
   </si>
   <si>
-    <t>60mg/1000mg mg/mg</t>
-  </si>
-  <si>
-    <t>8mg/500mg mg/mg</t>
-  </si>
-  <si>
     <t>Migraleve Yellow</t>
   </si>
   <si>
@@ -525,13 +514,7 @@
     <t>Dihyrdrocodeine with Paracetamol</t>
   </si>
   <si>
-    <t>10mg/500mg mg/mg</t>
-  </si>
-  <si>
     <t>Eroset</t>
-  </si>
-  <si>
-    <t>20mg/500mg mg/mg</t>
   </si>
   <si>
     <t>Remedeine</t>
@@ -772,6 +755,30 @@
   </si>
   <si>
     <t>UnitCost</t>
+  </si>
+  <si>
+    <t>12.8mg/500mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15mg/500mg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30mg/500mg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">60mg/1000mg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8mg/500mg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10mg/500mg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20mg/500mg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8mg/500mg </t>
   </si>
 </sst>
 </file>
@@ -1157,6 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J407"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1193,16 +1201,16 @@
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="22.5" customHeight="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
@@ -1233,7 +1241,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="22.5" customHeight="1">
+    <row r="3" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
@@ -1264,7 +1272,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="22.5" customHeight="1">
+    <row r="4" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -1295,7 +1303,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="22.5" customHeight="1">
+    <row r="5" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
@@ -1326,7 +1334,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="22.5" customHeight="1">
+    <row r="6" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -1357,7 +1365,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="22.5" customHeight="1">
+    <row r="7" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
@@ -1388,7 +1396,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="22.5" customHeight="1">
+    <row r="8" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>15</v>
       </c>
@@ -1421,7 +1429,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="22.5" customHeight="1">
+    <row r="9" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>20</v>
       </c>
@@ -1454,7 +1462,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="22.5" customHeight="1">
+    <row r="10" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
@@ -1487,7 +1495,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="22.5" customHeight="1">
+    <row r="11" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>27</v>
       </c>
@@ -1520,7 +1528,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="22.5" customHeight="1">
+    <row r="12" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
@@ -1553,7 +1561,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="22.5" customHeight="1">
+    <row r="13" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>27</v>
       </c>
@@ -1586,7 +1594,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="22.5" customHeight="1">
+    <row r="14" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>32</v>
       </c>
@@ -1619,7 +1627,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="22.5" customHeight="1">
+    <row r="15" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>35</v>
       </c>
@@ -1652,7 +1660,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="22.5" customHeight="1">
+    <row r="16" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>39</v>
       </c>
@@ -1685,7 +1693,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="22.5" customHeight="1">
+    <row r="17" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>39</v>
       </c>
@@ -1718,7 +1726,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="22.5" customHeight="1">
+    <row r="18" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
@@ -1751,7 +1759,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="22.5" customHeight="1">
+    <row r="19" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>39</v>
       </c>
@@ -1784,7 +1792,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="22.5" customHeight="1">
+    <row r="20" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>39</v>
       </c>
@@ -1817,7 +1825,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="22.5" customHeight="1">
+    <row r="21" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>39</v>
       </c>
@@ -1850,7 +1858,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="22.5" customHeight="1">
+    <row r="22" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>39</v>
       </c>
@@ -1883,7 +1891,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="22.5" customHeight="1">
+    <row r="23" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>39</v>
       </c>
@@ -1916,7 +1924,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="22.5" customHeight="1">
+    <row r="24" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>39</v>
       </c>
@@ -1949,7 +1957,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="22.5" customHeight="1">
+    <row r="25" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>50</v>
       </c>
@@ -1982,7 +1990,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="22.5" customHeight="1">
+    <row r="26" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>50</v>
       </c>
@@ -2015,7 +2023,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="22.5" customHeight="1">
+    <row r="27" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>50</v>
       </c>
@@ -2048,7 +2056,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="22.5" customHeight="1">
+    <row r="28" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>50</v>
       </c>
@@ -2081,7 +2089,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="22.5" customHeight="1">
+    <row r="29" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>50</v>
       </c>
@@ -2114,7 +2122,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="22.5" customHeight="1">
+    <row r="30" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>50</v>
       </c>
@@ -2147,7 +2155,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="22.5" customHeight="1">
+    <row r="31" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>50</v>
       </c>
@@ -2180,7 +2188,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="22.5" customHeight="1">
+    <row r="32" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A32" s="8" t="s">
         <v>50</v>
       </c>
@@ -2213,7 +2221,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="22.5" customHeight="1">
+    <row r="33" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A33" s="8" t="s">
         <v>50</v>
       </c>
@@ -2246,7 +2254,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="22.5" customHeight="1">
+    <row r="34" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>50</v>
       </c>
@@ -2279,7 +2287,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="22.5" customHeight="1">
+    <row r="35" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>50</v>
       </c>
@@ -2312,7 +2320,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="22.5" customHeight="1">
+    <row r="36" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="8" t="s">
         <v>50</v>
       </c>
@@ -2345,7 +2353,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="22.5" customHeight="1">
+    <row r="37" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>66</v>
       </c>
@@ -2378,7 +2386,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="22.5" customHeight="1">
+    <row r="38" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A38" s="8" t="s">
         <v>66</v>
       </c>
@@ -2411,7 +2419,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="22.5" customHeight="1">
+    <row r="39" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A39" s="8" t="s">
         <v>66</v>
       </c>
@@ -2444,7 +2452,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="22.5" customHeight="1">
+    <row r="40" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A40" s="8" t="s">
         <v>66</v>
       </c>
@@ -2477,7 +2485,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="22.5" customHeight="1">
+    <row r="41" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A41" s="8" t="s">
         <v>66</v>
       </c>
@@ -2510,7 +2518,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="22.5" customHeight="1">
+    <row r="42" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A42" s="8" t="s">
         <v>66</v>
       </c>
@@ -2543,7 +2551,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="22.5" customHeight="1">
+    <row r="43" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>66</v>
       </c>
@@ -2576,7 +2584,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="22.5" customHeight="1">
+    <row r="44" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A44" s="8" t="s">
         <v>66</v>
       </c>
@@ -2609,7 +2617,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="22.5" customHeight="1">
+    <row r="45" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A45" s="8" t="s">
         <v>66</v>
       </c>
@@ -2642,7 +2650,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="22.5" customHeight="1">
+    <row r="46" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A46" s="8" t="s">
         <v>66</v>
       </c>
@@ -2675,7 +2683,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="22.5" customHeight="1">
+    <row r="47" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>66</v>
       </c>
@@ -2708,7 +2716,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="22.5" customHeight="1">
+    <row r="48" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A48" s="8" t="s">
         <v>66</v>
       </c>
@@ -2741,7 +2749,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="22.5" customHeight="1">
+    <row r="49" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A49" s="8" t="s">
         <v>69</v>
       </c>
@@ -2774,7 +2782,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="22.5" customHeight="1">
+    <row r="50" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A50" s="8" t="s">
         <v>69</v>
       </c>
@@ -2807,7 +2815,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="22.5" customHeight="1">
+    <row r="51" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A51" s="8" t="s">
         <v>69</v>
       </c>
@@ -2840,7 +2848,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="22.5" customHeight="1">
+    <row r="52" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A52" s="8" t="s">
         <v>71</v>
       </c>
@@ -2873,7 +2881,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="22.5" customHeight="1">
+    <row r="53" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A53" s="8" t="s">
         <v>71</v>
       </c>
@@ -2906,7 +2914,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="22.5" customHeight="1">
+    <row r="54" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A54" s="8" t="s">
         <v>71</v>
       </c>
@@ -2939,7 +2947,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="22.5" customHeight="1">
+    <row r="55" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A55" s="8" t="s">
         <v>71</v>
       </c>
@@ -2972,7 +2980,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="22.5" customHeight="1">
+    <row r="56" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A56" s="8" t="s">
         <v>20</v>
       </c>
@@ -3005,7 +3013,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="22.5" customHeight="1">
+    <row r="57" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A57" s="8" t="s">
         <v>20</v>
       </c>
@@ -3038,7 +3046,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="22.5" customHeight="1">
+    <row r="58" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A58" s="8" t="s">
         <v>20</v>
       </c>
@@ -3071,7 +3079,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="22.5" customHeight="1">
+    <row r="59" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A59" s="8" t="s">
         <v>20</v>
       </c>
@@ -3104,7 +3112,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="22.5" customHeight="1">
+    <row r="60" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A60" s="8" t="s">
         <v>20</v>
       </c>
@@ -3137,7 +3145,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="22.5" customHeight="1">
+    <row r="61" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A61" s="8" t="s">
         <v>23</v>
       </c>
@@ -3170,7 +3178,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="22.5" customHeight="1">
+    <row r="62" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A62" s="8" t="s">
         <v>82</v>
       </c>
@@ -3203,7 +3211,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="22.5" customHeight="1">
+    <row r="63" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A63" s="8" t="s">
         <v>82</v>
       </c>
@@ -3236,7 +3244,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="22.5" customHeight="1">
+    <row r="64" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A64" s="8" t="s">
         <v>82</v>
       </c>
@@ -3269,7 +3277,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="22.5" customHeight="1">
+    <row r="65" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A65" s="8" t="s">
         <v>82</v>
       </c>
@@ -3302,7 +3310,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="22.5" customHeight="1">
+    <row r="66" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A66" s="8" t="s">
         <v>82</v>
       </c>
@@ -3335,7 +3343,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="22.5" customHeight="1">
+    <row r="67" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A67" s="8" t="s">
         <v>82</v>
       </c>
@@ -3368,7 +3376,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="22.5" customHeight="1">
+    <row r="68" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A68" s="8" t="s">
         <v>82</v>
       </c>
@@ -3401,7 +3409,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="22.5" customHeight="1">
+    <row r="69" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A69" s="8" t="s">
         <v>82</v>
       </c>
@@ -3434,7 +3442,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="22.5" customHeight="1">
+    <row r="70" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A70" s="8" t="s">
         <v>82</v>
       </c>
@@ -3467,7 +3475,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="22.5" customHeight="1">
+    <row r="71" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A71" s="8" t="s">
         <v>82</v>
       </c>
@@ -3500,7 +3508,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="22.5" customHeight="1">
+    <row r="72" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A72" s="8" t="s">
         <v>82</v>
       </c>
@@ -3533,7 +3541,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="22.5" customHeight="1">
+    <row r="73" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A73" s="8" t="s">
         <v>82</v>
       </c>
@@ -3566,7 +3574,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="22.5" customHeight="1">
+    <row r="74" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A74" s="8" t="s">
         <v>82</v>
       </c>
@@ -3599,7 +3607,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="22.5" customHeight="1">
+    <row r="75" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A75" s="8" t="s">
         <v>82</v>
       </c>
@@ -3632,7 +3640,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="22.5" customHeight="1">
+    <row r="76" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A76" s="8" t="s">
         <v>82</v>
       </c>
@@ -3665,7 +3673,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="22.5" customHeight="1">
+    <row r="77" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A77" s="8" t="s">
         <v>82</v>
       </c>
@@ -3698,7 +3706,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="22.5" customHeight="1">
+    <row r="78" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A78" s="8" t="s">
         <v>50</v>
       </c>
@@ -3731,7 +3739,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="22.5" customHeight="1">
+    <row r="79" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A79" s="8" t="s">
         <v>50</v>
       </c>
@@ -3764,7 +3772,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="22.5" customHeight="1">
+    <row r="80" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A80" s="8" t="s">
         <v>50</v>
       </c>
@@ -3797,7 +3805,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="22.5" customHeight="1">
+    <row r="81" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A81" s="8" t="s">
         <v>50</v>
       </c>
@@ -3830,7 +3838,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="22.5" customHeight="1">
+    <row r="82" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A82" s="8" t="s">
         <v>50</v>
       </c>
@@ -3863,7 +3871,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="22.5" customHeight="1">
+    <row r="83" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A83" s="8" t="s">
         <v>50</v>
       </c>
@@ -3896,7 +3904,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="22.5" customHeight="1">
+    <row r="84" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A84" s="8" t="s">
         <v>50</v>
       </c>
@@ -3929,7 +3937,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="22.5" customHeight="1">
+    <row r="85" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A85" s="8" t="s">
         <v>50</v>
       </c>
@@ -3962,7 +3970,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="22.5" customHeight="1">
+    <row r="86" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A86" s="8" t="s">
         <v>66</v>
       </c>
@@ -3995,7 +4003,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="22.5" customHeight="1">
+    <row r="87" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A87" s="8" t="s">
         <v>66</v>
       </c>
@@ -4028,7 +4036,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="22.5" customHeight="1">
+    <row r="88" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A88" s="8" t="s">
         <v>66</v>
       </c>
@@ -4061,7 +4069,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="22.5" customHeight="1">
+    <row r="89" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A89" s="8" t="s">
         <v>66</v>
       </c>
@@ -4094,7 +4102,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="22.5" customHeight="1">
+    <row r="90" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A90" s="8" t="s">
         <v>66</v>
       </c>
@@ -4127,7 +4135,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="22.5" customHeight="1">
+    <row r="91" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A91" s="8" t="s">
         <v>66</v>
       </c>
@@ -4160,7 +4168,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="22.5" customHeight="1">
+    <row r="92" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A92" s="8" t="s">
         <v>88</v>
       </c>
@@ -4193,7 +4201,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="22.5" customHeight="1">
+    <row r="93" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A93" s="8" t="s">
         <v>88</v>
       </c>
@@ -4226,7 +4234,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="22.5" customHeight="1">
+    <row r="94" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A94" s="8" t="s">
         <v>71</v>
       </c>
@@ -4259,7 +4267,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="22.5" customHeight="1">
+    <row r="95" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A95" s="8" t="s">
         <v>15</v>
       </c>
@@ -4267,7 +4275,7 @@
         <v>91</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8" t="s">
@@ -4290,7 +4298,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="22.5" customHeight="1">
+    <row r="96" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A96" s="8" t="s">
         <v>15</v>
       </c>
@@ -4321,7 +4329,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="22.5" customHeight="1">
+    <row r="97" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A97" s="8" t="s">
         <v>15</v>
       </c>
@@ -4352,7 +4360,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="22.5" customHeight="1">
+    <row r="98" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A98" s="8" t="s">
         <v>15</v>
       </c>
@@ -4360,7 +4368,7 @@
         <v>91</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D98" s="8"/>
       <c r="E98" s="8" t="s">
@@ -4383,7 +4391,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="22.5" customHeight="1">
+    <row r="99" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A99" s="8" t="s">
         <v>15</v>
       </c>
@@ -4414,7 +4422,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="22.5" customHeight="1">
+    <row r="100" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A100" s="8" t="s">
         <v>15</v>
       </c>
@@ -4422,7 +4430,7 @@
         <v>91</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8" t="s">
@@ -4445,7 +4453,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="22.5" customHeight="1">
+    <row r="101" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A101" s="8" t="s">
         <v>15</v>
       </c>
@@ -4476,7 +4484,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="22.5" customHeight="1">
+    <row r="102" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A102" s="8" t="s">
         <v>15</v>
       </c>
@@ -4507,7 +4515,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="22.5" customHeight="1">
+    <row r="103" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A103" s="8" t="s">
         <v>15</v>
       </c>
@@ -4538,7 +4546,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="22.5" customHeight="1">
+    <row r="104" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A104" s="8" t="s">
         <v>15</v>
       </c>
@@ -4569,7 +4577,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="22.5" customHeight="1">
+    <row r="105" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A105" s="8" t="s">
         <v>15</v>
       </c>
@@ -4600,7 +4608,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="22.5" customHeight="1">
+    <row r="106" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A106" s="8" t="s">
         <v>15</v>
       </c>
@@ -4631,7 +4639,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="22.5" customHeight="1">
+    <row r="107" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A107" s="8" t="s">
         <v>15</v>
       </c>
@@ -4662,7 +4670,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="22.5" customHeight="1">
+    <row r="108" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A108" s="8" t="s">
         <v>15</v>
       </c>
@@ -4693,7 +4701,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="22.5" customHeight="1">
+    <row r="109" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A109" s="8" t="s">
         <v>15</v>
       </c>
@@ -4724,7 +4732,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="22.5" customHeight="1">
+    <row r="110" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A110" s="8" t="s">
         <v>15</v>
       </c>
@@ -4755,7 +4763,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="22.5" customHeight="1">
+    <row r="111" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A111" s="8" t="s">
         <v>15</v>
       </c>
@@ -4786,7 +4794,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="22.5" customHeight="1">
+    <row r="112" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A112" s="8" t="s">
         <v>15</v>
       </c>
@@ -4817,7 +4825,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="22.5" customHeight="1">
+    <row r="113" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A113" s="8" t="s">
         <v>15</v>
       </c>
@@ -4848,7 +4856,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="22.5" customHeight="1">
+    <row r="114" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A114" s="8" t="s">
         <v>15</v>
       </c>
@@ -4879,7 +4887,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="22.5" customHeight="1">
+    <row r="115" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A115" s="8" t="s">
         <v>15</v>
       </c>
@@ -4910,7 +4918,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="22.5" customHeight="1">
+    <row r="116" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A116" s="8" t="s">
         <v>15</v>
       </c>
@@ -4941,7 +4949,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="22.5" customHeight="1">
+    <row r="117" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A117" s="8" t="s">
         <v>15</v>
       </c>
@@ -4972,7 +4980,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="22.5" customHeight="1">
+    <row r="118" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A118" s="8" t="s">
         <v>15</v>
       </c>
@@ -5003,7 +5011,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="22.5" customHeight="1">
+    <row r="119" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A119" s="8" t="s">
         <v>15</v>
       </c>
@@ -5034,7 +5042,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="22.5" customHeight="1">
+    <row r="120" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A120" s="8" t="s">
         <v>15</v>
       </c>
@@ -5065,7 +5073,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="22.5" customHeight="1">
+    <row r="121" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A121" s="8" t="s">
         <v>15</v>
       </c>
@@ -5096,7 +5104,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="22.5" customHeight="1">
+    <row r="122" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A122" s="8" t="s">
         <v>15</v>
       </c>
@@ -5127,7 +5135,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="22.5" customHeight="1">
+    <row r="123" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A123" s="8" t="s">
         <v>15</v>
       </c>
@@ -5158,7 +5166,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="22.5" customHeight="1">
+    <row r="124" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A124" s="8" t="s">
         <v>15</v>
       </c>
@@ -5189,7 +5197,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="22.5" customHeight="1">
+    <row r="125" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A125" s="8" t="s">
         <v>15</v>
       </c>
@@ -5220,7 +5228,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="22.5" customHeight="1">
+    <row r="126" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A126" s="8" t="s">
         <v>15</v>
       </c>
@@ -5251,7 +5259,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="22.5" customHeight="1">
+    <row r="127" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A127" s="8" t="s">
         <v>15</v>
       </c>
@@ -5282,7 +5290,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="22.5" customHeight="1">
+    <row r="128" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A128" s="8" t="s">
         <v>15</v>
       </c>
@@ -5313,7 +5321,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="22.5" customHeight="1">
+    <row r="129" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A129" s="8" t="s">
         <v>15</v>
       </c>
@@ -5344,7 +5352,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="22.5" customHeight="1">
+    <row r="130" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A130" s="8" t="s">
         <v>15</v>
       </c>
@@ -5375,7 +5383,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="22.5" customHeight="1">
+    <row r="131" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A131" s="8" t="s">
         <v>27</v>
       </c>
@@ -5406,7 +5414,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="22.5" customHeight="1">
+    <row r="132" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A132" s="8" t="s">
         <v>27</v>
       </c>
@@ -5437,7 +5445,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="22.5" customHeight="1">
+    <row r="133" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A133" s="8" t="s">
         <v>27</v>
       </c>
@@ -5468,7 +5476,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="22.5" customHeight="1">
+    <row r="134" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A134" s="8" t="s">
         <v>27</v>
       </c>
@@ -5499,7 +5507,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="22.5" customHeight="1">
+    <row r="135" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A135" s="8" t="s">
         <v>27</v>
       </c>
@@ -5530,7 +5538,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="22.5" customHeight="1">
+    <row r="136" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A136" s="8" t="s">
         <v>27</v>
       </c>
@@ -5561,7 +5569,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="22.5" customHeight="1">
+    <row r="137" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A137" s="8" t="s">
         <v>27</v>
       </c>
@@ -5590,7 +5598,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="22.5" customHeight="1">
+    <row r="138" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A138" s="8" t="s">
         <v>27</v>
       </c>
@@ -5619,7 +5627,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="22.5" customHeight="1">
+    <row r="139" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A139" s="8" t="s">
         <v>27</v>
       </c>
@@ -5627,7 +5635,7 @@
         <v>91</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8" t="s">
@@ -5650,7 +5658,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="22.5" customHeight="1">
+    <row r="140" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A140" s="8" t="s">
         <v>27</v>
       </c>
@@ -5681,7 +5689,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="22.5" customHeight="1">
+    <row r="141" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A141" s="8" t="s">
         <v>27</v>
       </c>
@@ -5712,7 +5720,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="22.5" customHeight="1">
+    <row r="142" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A142" s="8" t="s">
         <v>27</v>
       </c>
@@ -5743,7 +5751,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="22.5" customHeight="1">
+    <row r="143" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A143" s="8" t="s">
         <v>27</v>
       </c>
@@ -5774,7 +5782,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="22.5" customHeight="1">
+    <row r="144" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A144" s="8" t="s">
         <v>27</v>
       </c>
@@ -5805,7 +5813,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="22.5" customHeight="1">
+    <row r="145" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A145" s="8" t="s">
         <v>27</v>
       </c>
@@ -5836,7 +5844,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="22.5" customHeight="1">
+    <row r="146" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A146" s="8" t="s">
         <v>27</v>
       </c>
@@ -5865,7 +5873,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="22.5" customHeight="1">
+    <row r="147" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A147" s="8" t="s">
         <v>27</v>
       </c>
@@ -5894,7 +5902,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="22.5" customHeight="1">
+    <row r="148" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A148" s="8" t="s">
         <v>27</v>
       </c>
@@ -5925,7 +5933,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="22.5" customHeight="1">
+    <row r="149" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A149" s="8" t="s">
         <v>27</v>
       </c>
@@ -5933,7 +5941,7 @@
         <v>91</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8" t="s">
@@ -5956,7 +5964,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="22.5" customHeight="1">
+    <row r="150" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A150" s="8" t="s">
         <v>27</v>
       </c>
@@ -5987,7 +5995,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="22.5" customHeight="1">
+    <row r="151" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A151" s="8" t="s">
         <v>27</v>
       </c>
@@ -6018,7 +6026,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="22.5" customHeight="1">
+    <row r="152" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A152" s="8" t="s">
         <v>27</v>
       </c>
@@ -6049,7 +6057,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="22.5" customHeight="1">
+    <row r="153" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A153" s="8" t="s">
         <v>27</v>
       </c>
@@ -6080,7 +6088,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="22.5" customHeight="1">
+    <row r="154" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A154" s="8" t="s">
         <v>27</v>
       </c>
@@ -6111,7 +6119,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="22.5" customHeight="1">
+    <row r="155" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A155" s="8" t="s">
         <v>27</v>
       </c>
@@ -6140,7 +6148,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="22.5" customHeight="1">
+    <row r="156" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A156" s="8" t="s">
         <v>27</v>
       </c>
@@ -6169,7 +6177,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="22.5" customHeight="1">
+    <row r="157" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A157" s="8" t="s">
         <v>27</v>
       </c>
@@ -6198,7 +6206,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="22.5" customHeight="1">
+    <row r="158" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A158" s="8" t="s">
         <v>27</v>
       </c>
@@ -6206,7 +6214,7 @@
         <v>91</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8" t="s">
@@ -6229,7 +6237,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="22.5" customHeight="1">
+    <row r="159" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A159" s="8" t="s">
         <v>27</v>
       </c>
@@ -6256,11 +6264,11 @@
         <v>46.99</v>
       </c>
       <c r="J159" s="11" t="str">
-        <f t="shared" ref="J159:J222" si="3">"per" &amp; " " &amp;B159</f>
+        <f t="shared" ref="J159:J199" si="3">"per" &amp; " " &amp;B159</f>
         <v>per Patch</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="22.5" customHeight="1">
+    <row r="160" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A160" s="8" t="s">
         <v>27</v>
       </c>
@@ -6291,7 +6299,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="22.5" customHeight="1">
+    <row r="161" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A161" s="8" t="s">
         <v>27</v>
       </c>
@@ -6322,7 +6330,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="22.5" customHeight="1">
+    <row r="162" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A162" s="8" t="s">
         <v>27</v>
       </c>
@@ -6353,7 +6361,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="22.5" customHeight="1">
+    <row r="163" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A163" s="8" t="s">
         <v>27</v>
       </c>
@@ -6384,7 +6392,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="22.5" customHeight="1">
+    <row r="164" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A164" s="8" t="s">
         <v>27</v>
       </c>
@@ -6413,7 +6421,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="22.5" customHeight="1">
+    <row r="165" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A165" s="8" t="s">
         <v>27</v>
       </c>
@@ -6442,7 +6450,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="22.5" customHeight="1">
+    <row r="166" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A166" s="8" t="s">
         <v>27</v>
       </c>
@@ -6471,7 +6479,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="39" customHeight="1">
+    <row r="167" spans="1:10" ht="39" hidden="1" customHeight="1">
       <c r="A167" s="8" t="s">
         <v>27</v>
       </c>
@@ -6479,7 +6487,7 @@
         <v>91</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8" t="s">
@@ -6502,7 +6510,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="22.5" customHeight="1">
+    <row r="168" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A168" s="8" t="s">
         <v>27</v>
       </c>
@@ -6533,7 +6541,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="22.5" customHeight="1">
+    <row r="169" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A169" s="8" t="s">
         <v>27</v>
       </c>
@@ -6564,7 +6572,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="22.5" customHeight="1">
+    <row r="170" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A170" s="8" t="s">
         <v>27</v>
       </c>
@@ -6595,7 +6603,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="22.5" customHeight="1">
+    <row r="171" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A171" s="8" t="s">
         <v>27</v>
       </c>
@@ -6626,7 +6634,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="22.5" customHeight="1">
+    <row r="172" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A172" s="8" t="s">
         <v>27</v>
       </c>
@@ -6657,7 +6665,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="22.5" customHeight="1">
+    <row r="173" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A173" s="8" t="s">
         <v>27</v>
       </c>
@@ -6688,7 +6696,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="22.5" customHeight="1">
+    <row r="174" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A174" s="8" t="s">
         <v>27</v>
       </c>
@@ -6719,7 +6727,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="22.5" customHeight="1">
+    <row r="175" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A175" s="8" t="s">
         <v>27</v>
       </c>
@@ -6771,7 +6779,7 @@
         <v>11</v>
       </c>
       <c r="H176" s="9">
-        <v>0.12571428571428572</v>
+        <v>0.125714285714286</v>
       </c>
       <c r="I176" s="9">
         <v>0.88</v>
@@ -7339,7 +7347,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="22.5" customHeight="1">
+    <row r="195" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A195" s="8" t="s">
         <v>141</v>
       </c>
@@ -7370,7 +7378,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="22.5" customHeight="1">
+    <row r="196" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A196" s="8" t="s">
         <v>141</v>
       </c>
@@ -7401,7 +7409,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="22.5" customHeight="1">
+    <row r="197" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A197" s="8" t="s">
         <v>141</v>
       </c>
@@ -7432,7 +7440,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="22.5" customHeight="1">
+    <row r="198" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A198" s="8" t="s">
         <v>141</v>
       </c>
@@ -7463,7 +7471,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="22.5" customHeight="1">
+    <row r="199" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A199" s="8" t="s">
         <v>141</v>
       </c>
@@ -7494,7 +7502,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="22.5" customHeight="1">
+    <row r="200" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A200" s="8" t="s">
         <v>145</v>
       </c>
@@ -7502,30 +7510,30 @@
         <v>9</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D200" s="8"/>
       <c r="E200" s="8" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="F200" s="9">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G200" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H200" s="9">
-        <v>0.18049999999999999</v>
+        <v>3.56E-2</v>
       </c>
       <c r="I200" s="9">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="J200" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" ref="J200:J224" si="4">"per" &amp; " " &amp;B200</f>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A201" s="8" t="s">
         <v>145</v>
       </c>
@@ -7533,30 +7541,30 @@
         <v>9</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D201" s="8"/>
       <c r="E201" s="8" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="F201" s="9">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G201" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H201" s="9">
-        <v>0.18049999999999999</v>
+        <v>3.27E-2</v>
       </c>
       <c r="I201" s="9">
-        <v>3.61</v>
+        <v>3.27</v>
       </c>
       <c r="J201" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A202" s="8" t="s">
         <v>145</v>
       </c>
@@ -7564,11 +7572,11 @@
         <v>9</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D202" s="8"/>
       <c r="E202" s="8" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="F202" s="9">
         <v>30</v>
@@ -7577,17 +7585,17 @@
         <v>11</v>
       </c>
       <c r="H202" s="9">
-        <v>0.155</v>
+        <v>3.2666666666666663E-2</v>
       </c>
       <c r="I202" s="9">
-        <v>4.6500000000000004</v>
+        <v>0.98</v>
       </c>
       <c r="J202" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A203" s="8" t="s">
         <v>145</v>
       </c>
@@ -7599,7 +7607,7 @@
       </c>
       <c r="D203" s="8"/>
       <c r="E203" s="8" t="s">
-        <v>149</v>
+        <v>228</v>
       </c>
       <c r="F203" s="9">
         <v>100</v>
@@ -7608,60 +7616,60 @@
         <v>11</v>
       </c>
       <c r="H203" s="9">
-        <v>3.56E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="I203" s="9">
-        <v>3.56</v>
+        <v>3.27</v>
       </c>
       <c r="J203" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A204" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D204" s="8"/>
       <c r="E204" s="8" t="s">
-        <v>149</v>
+        <v>228</v>
       </c>
       <c r="F204" s="9">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="G204" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H204" s="9">
-        <v>3.56E-2</v>
+        <v>7.3124999999999996E-2</v>
       </c>
       <c r="I204" s="9">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="J204" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Efferevescent tablet</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A205" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D205" s="8"/>
       <c r="E205" s="8" t="s">
-        <v>149</v>
+        <v>228</v>
       </c>
       <c r="F205" s="9">
         <v>100</v>
@@ -7670,17 +7678,17 @@
         <v>11</v>
       </c>
       <c r="H205" s="9">
-        <v>8.2500000000000004E-2</v>
+        <v>7.3099999999999998E-2</v>
       </c>
       <c r="I205" s="9">
-        <v>8.25</v>
+        <v>7.31</v>
       </c>
       <c r="J205" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="22.5" customHeight="1">
+    <row r="206" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A206" s="8" t="s">
         <v>145</v>
       </c>
@@ -7692,7 +7700,7 @@
       </c>
       <c r="D206" s="8"/>
       <c r="E206" s="8" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="F206" s="9">
         <v>100</v>
@@ -7701,17 +7709,17 @@
         <v>11</v>
       </c>
       <c r="H206" s="9">
-        <v>3.27E-2</v>
+        <v>0.11849999999999999</v>
       </c>
       <c r="I206" s="9">
-        <v>3.27</v>
+        <v>11.85</v>
       </c>
       <c r="J206" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A207" s="8" t="s">
         <v>145</v>
       </c>
@@ -7723,26 +7731,26 @@
       </c>
       <c r="D207" s="8"/>
       <c r="E207" s="8" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="F207" s="9">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="G207" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H207" s="9">
-        <v>3.2666666666666663E-2</v>
+        <v>2.4700000000000003E-2</v>
       </c>
       <c r="I207" s="9">
-        <v>0.98</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="J207" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A208" s="8" t="s">
         <v>145</v>
       </c>
@@ -7754,26 +7762,26 @@
       </c>
       <c r="D208" s="8"/>
       <c r="E208" s="8" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="F208" s="9">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G208" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H208" s="9">
-        <v>3.27E-2</v>
+        <v>2.63E-2</v>
       </c>
       <c r="I208" s="9">
-        <v>3.27</v>
+        <v>13.15</v>
       </c>
       <c r="J208" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A209" s="8" t="s">
         <v>145</v>
       </c>
@@ -7781,30 +7789,30 @@
         <v>9</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D209" s="8"/>
       <c r="E209" s="8" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="F209" s="9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G209" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H209" s="9">
-        <v>3.27E-2</v>
+        <v>2.63E-2</v>
       </c>
       <c r="I209" s="9">
-        <v>3.27</v>
+        <v>26.3</v>
       </c>
       <c r="J209" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A210" s="8" t="s">
         <v>145</v>
       </c>
@@ -7812,42 +7820,42 @@
         <v>9</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D210" s="8"/>
       <c r="E210" s="8" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="F210" s="9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G210" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H210" s="9">
-        <v>3.2666666666666663E-2</v>
+        <v>2.7968750000000001E-2</v>
       </c>
       <c r="I210" s="9">
-        <v>0.98</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="J210" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A211" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D211" s="8"/>
       <c r="E211" s="8" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="F211" s="9">
         <v>100</v>
@@ -7856,17 +7864,17 @@
         <v>11</v>
       </c>
       <c r="H211" s="9">
-        <v>3.27E-2</v>
+        <v>6.6600000000000006E-2</v>
       </c>
       <c r="I211" s="9">
-        <v>3.27</v>
+        <v>6.66</v>
       </c>
       <c r="J211" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Efferevescent tablet</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A212" s="8" t="s">
         <v>145</v>
       </c>
@@ -7874,11 +7882,11 @@
         <v>9</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D212" s="8"/>
       <c r="E212" s="8" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F212" s="9">
         <v>100</v>
@@ -7887,60 +7895,60 @@
         <v>11</v>
       </c>
       <c r="H212" s="9">
-        <v>3.27E-2</v>
+        <v>3.56E-2</v>
       </c>
       <c r="I212" s="9">
-        <v>3.27</v>
+        <v>3.56</v>
       </c>
       <c r="J212" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A213" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D213" s="8"/>
       <c r="E213" s="8" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="F213" s="9">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G213" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H213" s="9">
-        <v>7.3124999999999996E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="I213" s="9">
-        <v>2.34</v>
+        <v>8.25</v>
       </c>
       <c r="J213" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="22.5" customHeight="1">
+    <row r="214" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A214" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D214" s="8"/>
       <c r="E214" s="8" t="s">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="F214" s="9">
         <v>100</v>
@@ -7949,110 +7957,110 @@
         <v>11</v>
       </c>
       <c r="H214" s="9">
-        <v>7.3099999999999998E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="I214" s="9">
-        <v>7.31</v>
+        <v>3.27</v>
       </c>
       <c r="J214" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Efferevescent tablet</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A215" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D215" s="8"/>
       <c r="E215" s="8" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="F215" s="9">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G215" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H215" s="9">
-        <v>7.3124999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="I215" s="9">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="J215" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Efferevescent tablet</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A216" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D216" s="8"/>
       <c r="E216" s="8" t="s">
-        <v>152</v>
+        <v>233</v>
       </c>
       <c r="F216" s="9">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G216" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H216" s="9">
-        <v>7.3099999999999998E-2</v>
+        <v>0.18049999999999999</v>
       </c>
       <c r="I216" s="9">
-        <v>7.31</v>
+        <v>3.61</v>
       </c>
       <c r="J216" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Efferevescent tablet</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A217" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D217" s="8"/>
       <c r="E217" s="8" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="F217" s="9">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="G217" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H217" s="9">
-        <v>0.11849999999999999</v>
+        <v>6.6562499999999997E-2</v>
       </c>
       <c r="I217" s="9">
-        <v>11.85</v>
+        <v>2.13</v>
       </c>
       <c r="J217" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Efferevescent tablet</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A218" s="8" t="s">
         <v>145</v>
       </c>
@@ -8060,30 +8068,30 @@
         <v>9</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D218" s="8"/>
       <c r="E218" s="8" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="F218" s="9">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G218" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H218" s="9">
-        <v>2.4700000000000003E-2</v>
+        <v>0.18049999999999999</v>
       </c>
       <c r="I218" s="9">
-        <v>2.4700000000000002</v>
+        <v>3.61</v>
       </c>
       <c r="J218" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A219" s="8" t="s">
         <v>145</v>
       </c>
@@ -8091,30 +8099,30 @@
         <v>9</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D219" s="8"/>
       <c r="E219" s="8" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="F219" s="9">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="G219" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H219" s="9">
-        <v>2.63E-2</v>
+        <v>0.155</v>
       </c>
       <c r="I219" s="9">
-        <v>13.15</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="J219" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A220" s="8" t="s">
         <v>145</v>
       </c>
@@ -8122,30 +8130,30 @@
         <v>9</v>
       </c>
       <c r="C220" s="8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D220" s="8"/>
       <c r="E220" s="8" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="F220" s="9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="G220" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H220" s="9">
-        <v>2.63E-2</v>
+        <v>3.2666666666666663E-2</v>
       </c>
       <c r="I220" s="9">
-        <v>26.3</v>
+        <v>0.98</v>
       </c>
       <c r="J220" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A221" s="8" t="s">
         <v>145</v>
       </c>
@@ -8153,73 +8161,73 @@
         <v>9</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D221" s="8"/>
       <c r="E221" s="8" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="F221" s="9">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G221" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H221" s="9">
-        <v>2.7968750000000001E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="I221" s="9">
-        <v>0.89500000000000002</v>
+        <v>3.27</v>
       </c>
       <c r="J221" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A222" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D222" s="8"/>
       <c r="E222" s="8" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="F222" s="9">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G222" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H222" s="9">
-        <v>0</v>
+        <v>7.3124999999999996E-2</v>
       </c>
       <c r="I222" s="9">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="J222" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="4"/>
+        <v>per Efferevescent tablet</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A223" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B223" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C223" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="C223" s="8" t="s">
-        <v>145</v>
       </c>
       <c r="D223" s="8"/>
       <c r="E223" s="8" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="F223" s="9">
         <v>100</v>
@@ -8228,60 +8236,60 @@
         <v>11</v>
       </c>
       <c r="H223" s="9">
-        <v>6.6600000000000006E-2</v>
+        <v>7.3099999999999998E-2</v>
       </c>
       <c r="I223" s="9">
-        <v>6.66</v>
+        <v>7.31</v>
       </c>
       <c r="J223" s="11" t="str">
-        <f t="shared" ref="J223:J286" si="4">"per" &amp; " " &amp;B223</f>
+        <f t="shared" si="4"/>
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="22.5" customHeight="1">
+    <row r="224" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A224" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D224" s="8"/>
       <c r="E224" s="8" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="F224" s="9">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G224" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H224" s="9">
-        <v>6.6562499999999997E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="I224" s="9">
-        <v>2.13</v>
+        <v>3.27</v>
       </c>
       <c r="J224" s="11" t="str">
         <f t="shared" si="4"/>
-        <v>per Efferevescent tablet</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" ht="22.5" customHeight="1">
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A225" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B225" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D225" s="8"/>
       <c r="E225" s="8" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="F225" s="9">
         <v>30</v>
@@ -8296,23 +8304,23 @@
         <v>0.71</v>
       </c>
       <c r="J225" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" ref="J225:J286" si="5">"per" &amp; " " &amp;B225</f>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A226" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B226" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D226" s="8"/>
       <c r="E226" s="8" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="F226" s="9">
         <v>100</v>
@@ -8327,23 +8335,23 @@
         <v>2.37</v>
       </c>
       <c r="J226" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A227" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B227" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D227" s="8"/>
       <c r="E227" s="8" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="F227" s="9">
         <v>500</v>
@@ -8358,23 +8366,23 @@
         <v>12.5</v>
       </c>
       <c r="J227" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A228" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B228" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D228" s="8"/>
       <c r="E228" s="8" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="F228" s="9">
         <v>30</v>
@@ -8389,23 +8397,23 @@
         <v>0.71</v>
       </c>
       <c r="J228" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A229" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B229" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D229" s="8"/>
       <c r="E229" s="8" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="F229" s="9">
         <v>100</v>
@@ -8420,23 +8428,23 @@
         <v>2.37</v>
       </c>
       <c r="J229" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A230" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B230" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D230" s="8"/>
       <c r="E230" s="8" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F230" s="9">
         <v>56</v>
@@ -8451,23 +8459,23 @@
         <v>5.7200000000000006</v>
       </c>
       <c r="J230" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A231" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B231" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D231" s="8"/>
       <c r="E231" s="8" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F231" s="9">
         <v>112</v>
@@ -8482,23 +8490,23 @@
         <v>11.13</v>
       </c>
       <c r="J231" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A232" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B232" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D232" s="8"/>
       <c r="E232" s="8" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F232" s="9">
         <v>56</v>
@@ -8513,23 +8521,23 @@
         <v>5.87</v>
       </c>
       <c r="J232" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A233" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B233" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D233" s="8"/>
       <c r="E233" s="8" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F233" s="9">
         <v>112</v>
@@ -8544,23 +8552,23 @@
         <v>11.13</v>
       </c>
       <c r="J233" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A234" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B234" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D234" s="8"/>
       <c r="E234" s="8" t="s">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="F234" s="9">
         <v>56</v>
@@ -8575,23 +8583,23 @@
         <v>6.82</v>
       </c>
       <c r="J234" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A235" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B235" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D235" s="8"/>
       <c r="E235" s="8" t="s">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="F235" s="9">
         <v>56</v>
@@ -8606,11 +8614,11 @@
         <v>6.82</v>
       </c>
       <c r="J235" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A236" s="8" t="s">
         <v>23</v>
       </c>
@@ -8618,7 +8626,7 @@
         <v>9</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D236" s="8"/>
       <c r="E236" s="8" t="s">
@@ -8637,11 +8645,11 @@
         <v>0.86</v>
       </c>
       <c r="J236" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A237" s="8" t="s">
         <v>23</v>
       </c>
@@ -8649,7 +8657,7 @@
         <v>9</v>
       </c>
       <c r="C237" s="8" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D237" s="8"/>
       <c r="E237" s="8" t="s">
@@ -8659,7 +8667,7 @@
         <v>30</v>
       </c>
       <c r="G237" s="9" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H237" s="9">
         <v>4.2666666666666665E-2</v>
@@ -8668,11 +8676,11 @@
         <v>1.28</v>
       </c>
       <c r="J237" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A238" s="8" t="s">
         <v>23</v>
       </c>
@@ -8680,7 +8688,7 @@
         <v>9</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D238" s="8"/>
       <c r="E238" s="8" t="s">
@@ -8699,11 +8707,11 @@
         <v>3.07</v>
       </c>
       <c r="J238" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A239" s="8" t="s">
         <v>23</v>
       </c>
@@ -8711,7 +8719,7 @@
         <v>9</v>
       </c>
       <c r="C239" s="8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D239" s="8"/>
       <c r="E239" s="8" t="s">
@@ -8730,11 +8738,11 @@
         <v>16.600000000000001</v>
       </c>
       <c r="J239" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A240" s="8" t="s">
         <v>23</v>
       </c>
@@ -8742,11 +8750,11 @@
         <v>9</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D240" s="8"/>
       <c r="E240" s="8" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F240" s="9">
         <v>100</v>
@@ -8761,11 +8769,11 @@
         <v>11.51</v>
       </c>
       <c r="J240" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A241" s="8" t="s">
         <v>23</v>
       </c>
@@ -8773,7 +8781,7 @@
         <v>9</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D241" s="8"/>
       <c r="E241" s="8" t="s">
@@ -8792,11 +8800,11 @@
         <v>5.2</v>
       </c>
       <c r="J241" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A242" s="8" t="s">
         <v>23</v>
       </c>
@@ -8804,11 +8812,11 @@
         <v>9</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D242" s="8"/>
       <c r="E242" s="8" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F242" s="9">
         <v>56</v>
@@ -8823,11 +8831,11 @@
         <v>8.66</v>
       </c>
       <c r="J242" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A243" s="8" t="s">
         <v>23</v>
       </c>
@@ -8835,11 +8843,11 @@
         <v>9</v>
       </c>
       <c r="C243" s="8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D243" s="8"/>
       <c r="E243" s="8" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F243" s="9">
         <v>56</v>
@@ -8854,11 +8862,11 @@
         <v>10.95</v>
       </c>
       <c r="J243" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A244" s="8" t="s">
         <v>27</v>
       </c>
@@ -8866,11 +8874,11 @@
         <v>9</v>
       </c>
       <c r="C244" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D244" s="8"/>
       <c r="E244" s="8" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F244" s="9">
         <v>4</v>
@@ -8885,11 +8893,11 @@
         <v>19.96</v>
       </c>
       <c r="J244" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A245" s="8" t="s">
         <v>27</v>
       </c>
@@ -8897,11 +8905,11 @@
         <v>9</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D245" s="8"/>
       <c r="E245" s="8" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F245" s="9">
         <v>28</v>
@@ -8916,11 +8924,11 @@
         <v>139.72</v>
       </c>
       <c r="J245" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="246" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A246" s="8" t="s">
         <v>27</v>
       </c>
@@ -8928,11 +8936,11 @@
         <v>9</v>
       </c>
       <c r="C246" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D246" s="8"/>
       <c r="E246" s="8" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F246" s="9">
         <v>10</v>
@@ -8947,11 +8955,11 @@
         <v>49.99</v>
       </c>
       <c r="J246" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="247" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A247" s="8" t="s">
         <v>27</v>
       </c>
@@ -8959,11 +8967,11 @@
         <v>9</v>
       </c>
       <c r="C247" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D247" s="8"/>
       <c r="E247" s="8" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F247" s="9">
         <v>30</v>
@@ -8978,11 +8986,11 @@
         <v>149.69999999999999</v>
       </c>
       <c r="J247" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="248" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A248" s="8" t="s">
         <v>27</v>
       </c>
@@ -8990,7 +8998,7 @@
         <v>9</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D248" s="8"/>
       <c r="E248" s="8" t="s">
@@ -9009,11 +9017,11 @@
         <v>19.96</v>
       </c>
       <c r="J248" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="249" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A249" s="8" t="s">
         <v>27</v>
       </c>
@@ -9021,7 +9029,7 @@
         <v>9</v>
       </c>
       <c r="C249" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D249" s="8"/>
       <c r="E249" s="8" t="s">
@@ -9040,11 +9048,11 @@
         <v>139.72</v>
       </c>
       <c r="J249" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A250" s="8" t="s">
         <v>27</v>
       </c>
@@ -9052,7 +9060,7 @@
         <v>9</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D250" s="8"/>
       <c r="E250" s="8" t="s">
@@ -9071,11 +9079,11 @@
         <v>49.99</v>
       </c>
       <c r="J250" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A251" s="8" t="s">
         <v>27</v>
       </c>
@@ -9083,7 +9091,7 @@
         <v>9</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D251" s="8"/>
       <c r="E251" s="8" t="s">
@@ -9102,11 +9110,11 @@
         <v>149.69999999999999</v>
       </c>
       <c r="J251" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A252" s="8" t="s">
         <v>27</v>
       </c>
@@ -9114,11 +9122,11 @@
         <v>9</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D252" s="8"/>
       <c r="E252" s="8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F252" s="9">
         <v>10</v>
@@ -9133,11 +9141,11 @@
         <v>49.99</v>
       </c>
       <c r="J252" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A253" s="8" t="s">
         <v>27</v>
       </c>
@@ -9145,11 +9153,11 @@
         <v>9</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D253" s="8"/>
       <c r="E253" s="8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F253" s="9">
         <v>30</v>
@@ -9164,11 +9172,11 @@
         <v>149.69999999999999</v>
       </c>
       <c r="J253" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A254" s="8" t="s">
         <v>27</v>
       </c>
@@ -9176,7 +9184,7 @@
         <v>9</v>
       </c>
       <c r="C254" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D254" s="8"/>
       <c r="E254" s="8" t="s">
@@ -9195,11 +9203,11 @@
         <v>19.96</v>
       </c>
       <c r="J254" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A255" s="8" t="s">
         <v>27</v>
       </c>
@@ -9207,7 +9215,7 @@
         <v>9</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D255" s="8"/>
       <c r="E255" s="8" t="s">
@@ -9226,11 +9234,11 @@
         <v>139.72</v>
       </c>
       <c r="J255" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A256" s="8" t="s">
         <v>27</v>
       </c>
@@ -9238,7 +9246,7 @@
         <v>9</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D256" s="8"/>
       <c r="E256" s="8" t="s">
@@ -9257,11 +9265,11 @@
         <v>49.99</v>
       </c>
       <c r="J256" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A257" s="8" t="s">
         <v>27</v>
       </c>
@@ -9269,7 +9277,7 @@
         <v>9</v>
       </c>
       <c r="C257" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D257" s="8"/>
       <c r="E257" s="8" t="s">
@@ -9288,11 +9296,11 @@
         <v>149.69999999999999</v>
       </c>
       <c r="J257" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="258" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A258" s="8" t="s">
         <v>27</v>
       </c>
@@ -9300,11 +9308,11 @@
         <v>9</v>
       </c>
       <c r="C258" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D258" s="8"/>
       <c r="E258" s="8" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F258" s="9">
         <v>4</v>
@@ -9319,11 +9327,11 @@
         <v>19.96</v>
       </c>
       <c r="J258" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A259" s="8" t="s">
         <v>27</v>
       </c>
@@ -9331,11 +9339,11 @@
         <v>9</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D259" s="8"/>
       <c r="E259" s="8" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F259" s="9">
         <v>28</v>
@@ -9350,11 +9358,11 @@
         <v>139.72</v>
       </c>
       <c r="J259" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A260" s="8" t="s">
         <v>27</v>
       </c>
@@ -9362,11 +9370,11 @@
         <v>9</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D260" s="8"/>
       <c r="E260" s="8" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F260" s="9">
         <v>30</v>
@@ -9381,11 +9389,11 @@
         <v>149.69999999999999</v>
       </c>
       <c r="J260" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="261" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A261" s="8" t="s">
         <v>27</v>
       </c>
@@ -9393,11 +9401,11 @@
         <v>9</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D261" s="8"/>
       <c r="E261" s="8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F261" s="9">
         <v>4</v>
@@ -9412,11 +9420,11 @@
         <v>19.96</v>
       </c>
       <c r="J261" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A262" s="8" t="s">
         <v>27</v>
       </c>
@@ -9424,11 +9432,11 @@
         <v>9</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D262" s="8"/>
       <c r="E262" s="8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F262" s="9">
         <v>28</v>
@@ -9443,11 +9451,11 @@
         <v>139.72</v>
       </c>
       <c r="J262" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A263" s="8" t="s">
         <v>27</v>
       </c>
@@ -9455,11 +9463,11 @@
         <v>9</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D263" s="8"/>
       <c r="E263" s="8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F263" s="9">
         <v>30</v>
@@ -9474,23 +9482,23 @@
         <v>149.69999999999999</v>
       </c>
       <c r="J263" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="264" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A264" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B264" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D264" s="8"/>
       <c r="E264" s="8" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F264" s="9">
         <v>56</v>
@@ -9505,19 +9513,19 @@
         <v>8.82</v>
       </c>
       <c r="J264" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="265" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A265" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B265" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D265" s="8"/>
       <c r="E265" s="8" t="s">
@@ -9536,23 +9544,23 @@
         <v>20.98</v>
       </c>
       <c r="J265" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="266" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A266" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B266" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D266" s="8"/>
       <c r="E266" s="8" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F266" s="9">
         <v>56</v>
@@ -9567,23 +9575,23 @@
         <v>17.64</v>
       </c>
       <c r="J266" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="267" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A267" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B267" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C267" s="8" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D267" s="8"/>
       <c r="E267" s="8" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F267" s="9">
         <v>56</v>
@@ -9598,19 +9606,19 @@
         <v>28.75</v>
       </c>
       <c r="J267" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="268" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A268" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B268" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C268" s="8" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D268" s="8"/>
       <c r="E268" s="8" t="s">
@@ -9629,23 +9637,23 @@
         <v>56.08</v>
       </c>
       <c r="J268" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="269" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A269" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B269" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D269" s="8"/>
       <c r="E269" s="8" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F269" s="9">
         <v>56</v>
@@ -9660,23 +9668,23 @@
         <v>106.53</v>
       </c>
       <c r="J269" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A270" s="8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B270" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C270" s="8" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D270" s="8"/>
       <c r="E270" s="8" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F270" s="9">
         <v>56</v>
@@ -9691,11 +9699,11 @@
         <v>159.82</v>
       </c>
       <c r="J270" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="271" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A271" s="8" t="s">
         <v>35</v>
       </c>
@@ -9707,7 +9715,7 @@
       </c>
       <c r="D271" s="8"/>
       <c r="E271" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F271" s="9">
         <v>112</v>
@@ -9722,11 +9730,11 @@
         <v>22.11</v>
       </c>
       <c r="J271" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="272" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A272" s="8" t="s">
         <v>82</v>
       </c>
@@ -9738,7 +9746,7 @@
       </c>
       <c r="D272" s="8"/>
       <c r="E272" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F272" s="9">
         <v>50</v>
@@ -9753,11 +9761,11 @@
         <v>2.84</v>
       </c>
       <c r="J272" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A273" s="8" t="s">
         <v>50</v>
       </c>
@@ -9765,11 +9773,11 @@
         <v>9</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D273" s="8"/>
       <c r="E273" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F273" s="9">
         <v>60</v>
@@ -9784,11 +9792,11 @@
         <v>3.29</v>
       </c>
       <c r="J273" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A274" s="8" t="s">
         <v>50</v>
       </c>
@@ -9796,11 +9804,11 @@
         <v>9</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D274" s="8"/>
       <c r="E274" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F274" s="9">
         <v>60</v>
@@ -9815,11 +9823,11 @@
         <v>5.2</v>
       </c>
       <c r="J274" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="275" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A275" s="8" t="s">
         <v>50</v>
       </c>
@@ -9827,11 +9835,11 @@
         <v>9</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D275" s="8"/>
       <c r="E275" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F275" s="9">
         <v>60</v>
@@ -9846,11 +9854,11 @@
         <v>5.2</v>
       </c>
       <c r="J275" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="276" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A276" s="8" t="s">
         <v>50</v>
       </c>
@@ -9858,11 +9866,11 @@
         <v>9</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D276" s="8"/>
       <c r="E276" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F276" s="9">
         <v>56</v>
@@ -9877,11 +9885,11 @@
         <v>5.31</v>
       </c>
       <c r="J276" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="277" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A277" s="8" t="s">
         <v>50</v>
       </c>
@@ -9889,7 +9897,7 @@
         <v>9</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D277" s="8"/>
       <c r="E277" s="8" t="s">
@@ -9908,11 +9916,11 @@
         <v>9.1</v>
       </c>
       <c r="J277" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="278" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A278" s="8" t="s">
         <v>50</v>
       </c>
@@ -9920,11 +9928,11 @@
         <v>9</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D278" s="8"/>
       <c r="E278" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F278" s="9">
         <v>56</v>
@@ -9939,11 +9947,11 @@
         <v>10.61</v>
       </c>
       <c r="J278" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A279" s="8" t="s">
         <v>50</v>
       </c>
@@ -9951,7 +9959,7 @@
         <v>9</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D279" s="8"/>
       <c r="E279" s="8" t="s">
@@ -9970,11 +9978,11 @@
         <v>12.47</v>
       </c>
       <c r="J279" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="280" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A280" s="8" t="s">
         <v>50</v>
       </c>
@@ -9982,7 +9990,7 @@
         <v>9</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D280" s="8"/>
       <c r="E280" s="8" t="s">
@@ -10001,11 +10009,11 @@
         <v>12.47</v>
       </c>
       <c r="J280" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A281" s="8" t="s">
         <v>50</v>
       </c>
@@ -10013,11 +10021,11 @@
         <v>9</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D281" s="8"/>
       <c r="E281" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F281" s="9">
         <v>56</v>
@@ -10032,11 +10040,11 @@
         <v>28.02</v>
       </c>
       <c r="J281" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="282" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A282" s="8" t="s">
         <v>50</v>
       </c>
@@ -10044,7 +10052,7 @@
         <v>9</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D282" s="8"/>
       <c r="E282" s="8" t="s">
@@ -10063,11 +10071,11 @@
         <v>24.32</v>
       </c>
       <c r="J282" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="283" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A283" s="8" t="s">
         <v>50</v>
       </c>
@@ -10075,7 +10083,7 @@
         <v>9</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D283" s="8"/>
       <c r="E283" s="8" t="s">
@@ -10094,11 +10102,11 @@
         <v>18.04</v>
       </c>
       <c r="J283" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A284" s="8" t="s">
         <v>50</v>
       </c>
@@ -10106,11 +10114,11 @@
         <v>9</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D284" s="8"/>
       <c r="E284" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F284" s="9">
         <v>60</v>
@@ -10125,11 +10133,11 @@
         <v>38.5</v>
       </c>
       <c r="J284" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="285" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A285" s="8" t="s">
         <v>50</v>
       </c>
@@ -10137,11 +10145,11 @@
         <v>9</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D285" s="8"/>
       <c r="E285" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F285" s="9">
         <v>60</v>
@@ -10156,11 +10164,11 @@
         <v>38.5</v>
       </c>
       <c r="J285" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="286" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A286" s="8" t="s">
         <v>50</v>
       </c>
@@ -10168,11 +10176,11 @@
         <v>9</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D286" s="8"/>
       <c r="E286" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F286" s="9">
         <v>60</v>
@@ -10187,11 +10195,11 @@
         <v>81.34</v>
       </c>
       <c r="J286" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="287" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A287" s="8" t="s">
         <v>66</v>
       </c>
@@ -10199,11 +10207,11 @@
         <v>9</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D287" s="8"/>
       <c r="E287" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F287" s="9">
         <v>28</v>
@@ -10218,11 +10226,11 @@
         <v>12.52</v>
       </c>
       <c r="J287" s="11" t="str">
-        <f t="shared" ref="J287:J350" si="5">"per" &amp; " " &amp;B287</f>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="288" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" ref="J287:J350" si="6">"per" &amp; " " &amp;B287</f>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A288" s="8" t="s">
         <v>66</v>
       </c>
@@ -10230,11 +10238,11 @@
         <v>9</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D288" s="8"/>
       <c r="E288" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F288" s="9">
         <v>28</v>
@@ -10249,11 +10257,11 @@
         <v>12.52</v>
       </c>
       <c r="J288" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="289" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A289" s="8" t="s">
         <v>66</v>
       </c>
@@ -10261,11 +10269,11 @@
         <v>9</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D289" s="8"/>
       <c r="E289" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F289" s="9">
         <v>28</v>
@@ -10280,11 +10288,11 @@
         <v>12.52</v>
       </c>
       <c r="J289" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A290" s="8" t="s">
         <v>66</v>
       </c>
@@ -10292,11 +10300,11 @@
         <v>9</v>
       </c>
       <c r="C290" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D290" s="8"/>
       <c r="E290" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F290" s="9">
         <v>28</v>
@@ -10311,11 +10319,11 @@
         <v>12.52</v>
       </c>
       <c r="J290" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A291" s="8" t="s">
         <v>66</v>
       </c>
@@ -10323,11 +10331,11 @@
         <v>9</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D291" s="8"/>
       <c r="E291" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F291" s="9">
         <v>28</v>
@@ -10342,11 +10350,11 @@
         <v>12.52</v>
       </c>
       <c r="J291" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A292" s="8" t="s">
         <v>66</v>
       </c>
@@ -10354,11 +10362,11 @@
         <v>9</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D292" s="8"/>
       <c r="E292" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F292" s="9">
         <v>28</v>
@@ -10373,11 +10381,11 @@
         <v>12.52</v>
       </c>
       <c r="J292" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A293" s="8" t="s">
         <v>66</v>
       </c>
@@ -10385,11 +10393,11 @@
         <v>9</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D293" s="8"/>
       <c r="E293" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F293" s="9">
         <v>28</v>
@@ -10404,11 +10412,11 @@
         <v>12.52</v>
       </c>
       <c r="J293" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="294" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A294" s="8" t="s">
         <v>66</v>
       </c>
@@ -10416,11 +10424,11 @@
         <v>9</v>
       </c>
       <c r="C294" s="8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D294" s="8"/>
       <c r="E294" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F294" s="9">
         <v>28</v>
@@ -10435,11 +10443,11 @@
         <v>12.52</v>
       </c>
       <c r="J294" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A295" s="8" t="s">
         <v>66</v>
       </c>
@@ -10447,11 +10455,11 @@
         <v>9</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D295" s="8"/>
       <c r="E295" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F295" s="9">
         <v>28</v>
@@ -10466,11 +10474,11 @@
         <v>12.52</v>
       </c>
       <c r="J295" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="296" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A296" s="8" t="s">
         <v>66</v>
       </c>
@@ -10478,11 +10486,11 @@
         <v>9</v>
       </c>
       <c r="C296" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D296" s="8"/>
       <c r="E296" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F296" s="9">
         <v>56</v>
@@ -10497,11 +10505,11 @@
         <v>25.04</v>
       </c>
       <c r="J296" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="297" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A297" s="8" t="s">
         <v>66</v>
       </c>
@@ -10509,11 +10517,11 @@
         <v>9</v>
       </c>
       <c r="C297" s="8" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D297" s="8"/>
       <c r="E297" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F297" s="9">
         <v>56</v>
@@ -10528,11 +10536,11 @@
         <v>25.04</v>
       </c>
       <c r="J297" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="298" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A298" s="8" t="s">
         <v>66</v>
       </c>
@@ -10540,11 +10548,11 @@
         <v>9</v>
       </c>
       <c r="C298" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D298" s="8"/>
       <c r="E298" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F298" s="9">
         <v>56</v>
@@ -10559,11 +10567,11 @@
         <v>25.04</v>
       </c>
       <c r="J298" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="299" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A299" s="8" t="s">
         <v>66</v>
       </c>
@@ -10571,11 +10579,11 @@
         <v>9</v>
       </c>
       <c r="C299" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D299" s="8"/>
       <c r="E299" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F299" s="9">
         <v>56</v>
@@ -10590,11 +10598,11 @@
         <v>25.04</v>
       </c>
       <c r="J299" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="300" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A300" s="8" t="s">
         <v>66</v>
       </c>
@@ -10602,11 +10610,11 @@
         <v>9</v>
       </c>
       <c r="C300" s="8" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D300" s="8"/>
       <c r="E300" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F300" s="9">
         <v>28</v>
@@ -10621,11 +10629,11 @@
         <v>12.52</v>
       </c>
       <c r="J300" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="301" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A301" s="8" t="s">
         <v>66</v>
       </c>
@@ -10633,11 +10641,11 @@
         <v>9</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D301" s="8"/>
       <c r="E301" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F301" s="9">
         <v>56</v>
@@ -10652,11 +10660,11 @@
         <v>25.04</v>
       </c>
       <c r="J301" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="302" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A302" s="8" t="s">
         <v>66</v>
       </c>
@@ -10664,11 +10672,11 @@
         <v>9</v>
       </c>
       <c r="C302" s="8" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D302" s="8"/>
       <c r="E302" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F302" s="9">
         <v>56</v>
@@ -10683,11 +10691,11 @@
         <v>25.04</v>
       </c>
       <c r="J302" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A303" s="8" t="s">
         <v>66</v>
       </c>
@@ -10695,11 +10703,11 @@
         <v>9</v>
       </c>
       <c r="C303" s="8" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D303" s="8"/>
       <c r="E303" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F303" s="9">
         <v>56</v>
@@ -10714,11 +10722,11 @@
         <v>25.04</v>
       </c>
       <c r="J303" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="304" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A304" s="8" t="s">
         <v>66</v>
       </c>
@@ -10726,11 +10734,11 @@
         <v>9</v>
       </c>
       <c r="C304" s="8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D304" s="8"/>
       <c r="E304" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F304" s="9">
         <v>56</v>
@@ -10745,11 +10753,11 @@
         <v>25.04</v>
       </c>
       <c r="J304" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="305" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A305" s="8" t="s">
         <v>66</v>
       </c>
@@ -10757,7 +10765,7 @@
         <v>9</v>
       </c>
       <c r="C305" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D305" s="8"/>
       <c r="E305" s="8" t="s">
@@ -10776,11 +10784,11 @@
         <v>38.119999999999997</v>
       </c>
       <c r="J305" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A306" s="8" t="s">
         <v>66</v>
       </c>
@@ -10788,7 +10796,7 @@
         <v>9</v>
       </c>
       <c r="C306" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D306" s="8"/>
       <c r="E306" s="8" t="s">
@@ -10807,11 +10815,11 @@
         <v>38.119999999999997</v>
       </c>
       <c r="J306" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="307" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A307" s="8" t="s">
         <v>66</v>
       </c>
@@ -10819,7 +10827,7 @@
         <v>9</v>
       </c>
       <c r="C307" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D307" s="8"/>
       <c r="E307" s="8" t="s">
@@ -10838,11 +10846,11 @@
         <v>38.119999999999997</v>
       </c>
       <c r="J307" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="308" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A308" s="8" t="s">
         <v>66</v>
       </c>
@@ -10850,7 +10858,7 @@
         <v>9</v>
       </c>
       <c r="C308" s="8" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D308" s="8"/>
       <c r="E308" s="8" t="s">
@@ -10869,11 +10877,11 @@
         <v>38.119999999999997</v>
       </c>
       <c r="J308" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="309" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A309" s="8" t="s">
         <v>66</v>
       </c>
@@ -10881,7 +10889,7 @@
         <v>9</v>
       </c>
       <c r="C309" s="8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D309" s="8"/>
       <c r="E309" s="8" t="s">
@@ -10900,11 +10908,11 @@
         <v>38.119999999999997</v>
       </c>
       <c r="J309" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="310" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A310" s="8" t="s">
         <v>66</v>
       </c>
@@ -10912,11 +10920,11 @@
         <v>9</v>
       </c>
       <c r="C310" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D310" s="8"/>
       <c r="E310" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F310" s="9">
         <v>56</v>
@@ -10931,11 +10939,11 @@
         <v>50.08</v>
       </c>
       <c r="J310" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A311" s="8" t="s">
         <v>66</v>
       </c>
@@ -10943,11 +10951,11 @@
         <v>9</v>
       </c>
       <c r="C311" s="8" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D311" s="8"/>
       <c r="E311" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F311" s="9">
         <v>56</v>
@@ -10962,11 +10970,11 @@
         <v>50.08</v>
       </c>
       <c r="J311" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="312" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A312" s="8" t="s">
         <v>66</v>
       </c>
@@ -10974,11 +10982,11 @@
         <v>9</v>
       </c>
       <c r="C312" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D312" s="8"/>
       <c r="E312" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F312" s="9">
         <v>56</v>
@@ -10993,11 +11001,11 @@
         <v>50.08</v>
       </c>
       <c r="J312" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="313" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A313" s="8" t="s">
         <v>66</v>
       </c>
@@ -11005,11 +11013,11 @@
         <v>9</v>
       </c>
       <c r="C313" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D313" s="8"/>
       <c r="E313" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F313" s="9">
         <v>56</v>
@@ -11024,11 +11032,11 @@
         <v>50.08</v>
       </c>
       <c r="J313" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="314" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A314" s="8" t="s">
         <v>66</v>
       </c>
@@ -11036,11 +11044,11 @@
         <v>9</v>
       </c>
       <c r="C314" s="8" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D314" s="8"/>
       <c r="E314" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F314" s="9">
         <v>28</v>
@@ -11055,11 +11063,11 @@
         <v>12.52</v>
       </c>
       <c r="J314" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="315" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A315" s="8" t="s">
         <v>66</v>
       </c>
@@ -11067,11 +11075,11 @@
         <v>9</v>
       </c>
       <c r="C315" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D315" s="8"/>
       <c r="E315" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F315" s="9">
         <v>56</v>
@@ -11086,11 +11094,11 @@
         <v>50.08</v>
       </c>
       <c r="J315" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="316" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A316" s="8" t="s">
         <v>66</v>
       </c>
@@ -11098,11 +11106,11 @@
         <v>9</v>
       </c>
       <c r="C316" s="8" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D316" s="8"/>
       <c r="E316" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F316" s="9">
         <v>56</v>
@@ -11117,11 +11125,11 @@
         <v>50.08</v>
       </c>
       <c r="J316" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A317" s="8" t="s">
         <v>66</v>
       </c>
@@ -11129,11 +11137,11 @@
         <v>9</v>
       </c>
       <c r="C317" s="8" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D317" s="8"/>
       <c r="E317" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F317" s="9">
         <v>56</v>
@@ -11148,11 +11156,11 @@
         <v>50.08</v>
       </c>
       <c r="J317" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="318" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A318" s="8" t="s">
         <v>66</v>
       </c>
@@ -11160,11 +11168,11 @@
         <v>9</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D318" s="8"/>
       <c r="E318" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F318" s="9">
         <v>56</v>
@@ -11179,11 +11187,11 @@
         <v>50.08</v>
       </c>
       <c r="J318" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="319" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A319" s="8" t="s">
         <v>66</v>
       </c>
@@ -11191,11 +11199,11 @@
         <v>9</v>
       </c>
       <c r="C319" s="8" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D319" s="8"/>
       <c r="E319" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F319" s="9">
         <v>56</v>
@@ -11210,11 +11218,11 @@
         <v>50.08</v>
       </c>
       <c r="J319" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="320" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A320" s="8" t="s">
         <v>66</v>
       </c>
@@ -11222,7 +11230,7 @@
         <v>9</v>
       </c>
       <c r="C320" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D320" s="8"/>
       <c r="E320" s="8" t="s">
@@ -11241,11 +11249,11 @@
         <v>76.23</v>
       </c>
       <c r="J320" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="321" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A321" s="8" t="s">
         <v>66</v>
       </c>
@@ -11253,7 +11261,7 @@
         <v>9</v>
       </c>
       <c r="C321" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D321" s="8"/>
       <c r="E321" s="8" t="s">
@@ -11272,11 +11280,11 @@
         <v>76.23</v>
       </c>
       <c r="J321" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="322" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A322" s="8" t="s">
         <v>66</v>
       </c>
@@ -11284,7 +11292,7 @@
         <v>9</v>
       </c>
       <c r="C322" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D322" s="8"/>
       <c r="E322" s="8" t="s">
@@ -11303,11 +11311,11 @@
         <v>76.23</v>
       </c>
       <c r="J322" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="323" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A323" s="8" t="s">
         <v>66</v>
       </c>
@@ -11315,7 +11323,7 @@
         <v>9</v>
       </c>
       <c r="C323" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D323" s="8"/>
       <c r="E323" s="8" t="s">
@@ -11334,11 +11342,11 @@
         <v>76.23</v>
       </c>
       <c r="J323" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="324" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A324" s="8" t="s">
         <v>66</v>
       </c>
@@ -11346,7 +11354,7 @@
         <v>9</v>
       </c>
       <c r="C324" s="8" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D324" s="8"/>
       <c r="E324" s="8" t="s">
@@ -11365,11 +11373,11 @@
         <v>76.23</v>
       </c>
       <c r="J324" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="325" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A325" s="8" t="s">
         <v>66</v>
       </c>
@@ -11377,7 +11385,7 @@
         <v>9</v>
       </c>
       <c r="C325" s="8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D325" s="8"/>
       <c r="E325" s="8" t="s">
@@ -11396,11 +11404,11 @@
         <v>76.23</v>
       </c>
       <c r="J325" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A326" s="8" t="s">
         <v>69</v>
       </c>
@@ -11412,7 +11420,7 @@
       </c>
       <c r="D326" s="8"/>
       <c r="E326" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F326" s="9">
         <v>50</v>
@@ -11427,11 +11435,11 @@
         <v>49.92</v>
       </c>
       <c r="J326" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="327" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A327" s="8" t="s">
         <v>88</v>
       </c>
@@ -11439,11 +11447,11 @@
         <v>9</v>
       </c>
       <c r="C327" s="8" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D327" s="8"/>
       <c r="E327" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F327" s="9">
         <v>28</v>
@@ -11458,11 +11466,11 @@
         <v>12.46</v>
       </c>
       <c r="J327" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="328" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A328" s="8" t="s">
         <v>88</v>
       </c>
@@ -11470,11 +11478,11 @@
         <v>9</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D328" s="8"/>
       <c r="E328" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F328" s="9">
         <v>56</v>
@@ -11489,11 +11497,11 @@
         <v>24.91</v>
       </c>
       <c r="J328" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="329" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A329" s="8" t="s">
         <v>88</v>
       </c>
@@ -11505,7 +11513,7 @@
       </c>
       <c r="D329" s="8"/>
       <c r="E329" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F329" s="9">
         <v>28</v>
@@ -11520,11 +11528,11 @@
         <v>12.46</v>
       </c>
       <c r="J329" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A330" s="8" t="s">
         <v>88</v>
       </c>
@@ -11536,7 +11544,7 @@
       </c>
       <c r="D330" s="8"/>
       <c r="E330" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F330" s="9">
         <v>56</v>
@@ -11551,11 +11559,11 @@
         <v>24.91</v>
       </c>
       <c r="J330" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A331" s="8" t="s">
         <v>88</v>
       </c>
@@ -11567,7 +11575,7 @@
       </c>
       <c r="D331" s="8"/>
       <c r="E331" s="8" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F331" s="9">
         <v>28</v>
@@ -11582,11 +11590,11 @@
         <v>18.68</v>
       </c>
       <c r="J331" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="332" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A332" s="8" t="s">
         <v>88</v>
       </c>
@@ -11598,7 +11606,7 @@
       </c>
       <c r="D332" s="8"/>
       <c r="E332" s="8" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F332" s="9">
         <v>56</v>
@@ -11613,11 +11621,11 @@
         <v>37.369999999999997</v>
       </c>
       <c r="J332" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="333" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A333" s="8" t="s">
         <v>88</v>
       </c>
@@ -11625,11 +11633,11 @@
         <v>9</v>
       </c>
       <c r="C333" s="8" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D333" s="8"/>
       <c r="E333" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F333" s="9">
         <v>56</v>
@@ -11644,11 +11652,11 @@
         <v>49.82</v>
       </c>
       <c r="J333" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="334" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A334" s="8" t="s">
         <v>88</v>
       </c>
@@ -11656,11 +11664,11 @@
         <v>9</v>
       </c>
       <c r="C334" s="8" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D334" s="8"/>
       <c r="E334" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F334" s="9">
         <v>56</v>
@@ -11675,11 +11683,11 @@
         <v>74.73</v>
       </c>
       <c r="J334" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="335" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A335" s="8" t="s">
         <v>88</v>
       </c>
@@ -11687,11 +11695,11 @@
         <v>9</v>
       </c>
       <c r="C335" s="8" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D335" s="8"/>
       <c r="E335" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F335" s="9">
         <v>56</v>
@@ -11706,11 +11714,11 @@
         <v>99.64</v>
       </c>
       <c r="J335" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="336" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A336" s="8" t="s">
         <v>88</v>
       </c>
@@ -11718,11 +11726,11 @@
         <v>9</v>
       </c>
       <c r="C336" s="8" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D336" s="8"/>
       <c r="E336" s="8" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F336" s="9">
         <v>56</v>
@@ -11737,11 +11745,11 @@
         <v>124.55</v>
       </c>
       <c r="J336" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="337" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A337" s="8" t="s">
         <v>71</v>
       </c>
@@ -11753,7 +11761,7 @@
       </c>
       <c r="D337" s="8"/>
       <c r="E337" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F337" s="9">
         <v>60</v>
@@ -11768,11 +11776,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="J337" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="338" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A338" s="8" t="s">
         <v>71</v>
       </c>
@@ -11784,7 +11792,7 @@
       </c>
       <c r="D338" s="8"/>
       <c r="E338" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F338" s="9">
         <v>20</v>
@@ -11799,11 +11807,11 @@
         <v>2.79</v>
       </c>
       <c r="J338" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="339" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A339" s="8" t="s">
         <v>71</v>
       </c>
@@ -11815,7 +11823,7 @@
       </c>
       <c r="D339" s="8"/>
       <c r="E339" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F339" s="9">
         <v>100</v>
@@ -11830,11 +11838,11 @@
         <v>13.33</v>
       </c>
       <c r="J339" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="340" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A340" s="8" t="s">
         <v>71</v>
       </c>
@@ -11842,11 +11850,11 @@
         <v>9</v>
       </c>
       <c r="C340" s="8" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D340" s="8"/>
       <c r="E340" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F340" s="9">
         <v>50</v>
@@ -11861,11 +11869,11 @@
         <v>7.12</v>
       </c>
       <c r="J340" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="341" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A341" s="8" t="s">
         <v>71</v>
       </c>
@@ -11873,11 +11881,11 @@
         <v>9</v>
       </c>
       <c r="C341" s="8" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D341" s="8"/>
       <c r="E341" s="8" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F341" s="9">
         <v>60</v>
@@ -11892,11 +11900,11 @@
         <v>5.15</v>
       </c>
       <c r="J341" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A342" s="8" t="s">
         <v>71</v>
       </c>
@@ -11904,11 +11912,11 @@
         <v>9</v>
       </c>
       <c r="C342" s="8" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D342" s="8"/>
       <c r="E342" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F342" s="9">
         <v>60</v>
@@ -11923,11 +11931,11 @@
         <v>18</v>
       </c>
       <c r="J342" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="343" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A343" s="8" t="s">
         <v>71</v>
       </c>
@@ -11935,11 +11943,11 @@
         <v>9</v>
       </c>
       <c r="C343" s="8" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D343" s="8"/>
       <c r="E343" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F343" s="9">
         <v>60</v>
@@ -11954,11 +11962,11 @@
         <v>5.55</v>
       </c>
       <c r="J343" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="344" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A344" s="8" t="s">
         <v>71</v>
       </c>
@@ -11966,11 +11974,11 @@
         <v>9</v>
       </c>
       <c r="C344" s="8" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D344" s="8"/>
       <c r="E344" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F344" s="9">
         <v>60</v>
@@ -11985,11 +11993,11 @@
         <v>15.52</v>
       </c>
       <c r="J344" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="345" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A345" s="8" t="s">
         <v>71</v>
       </c>
@@ -11997,11 +12005,11 @@
         <v>9</v>
       </c>
       <c r="C345" s="8" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D345" s="8"/>
       <c r="E345" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F345" s="9">
         <v>60</v>
@@ -12016,11 +12024,11 @@
         <v>6.95</v>
       </c>
       <c r="J345" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A346" s="8" t="s">
         <v>71</v>
       </c>
@@ -12028,11 +12036,11 @@
         <v>9</v>
       </c>
       <c r="C346" s="8" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D346" s="8"/>
       <c r="E346" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F346" s="9">
         <v>60</v>
@@ -12047,11 +12055,11 @@
         <v>6.94</v>
       </c>
       <c r="J346" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="347" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A347" s="8" t="s">
         <v>71</v>
       </c>
@@ -12059,11 +12067,11 @@
         <v>9</v>
       </c>
       <c r="C347" s="8" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D347" s="8"/>
       <c r="E347" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F347" s="9">
         <v>60</v>
@@ -12078,11 +12086,11 @@
         <v>15.52</v>
       </c>
       <c r="J347" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="348" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A348" s="8" t="s">
         <v>71</v>
       </c>
@@ -12090,11 +12098,11 @@
         <v>9</v>
       </c>
       <c r="C348" s="8" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D348" s="8"/>
       <c r="E348" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F348" s="9">
         <v>30</v>
@@ -12109,11 +12117,11 @@
         <v>14.1</v>
       </c>
       <c r="J348" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="349" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A349" s="8" t="s">
         <v>71</v>
       </c>
@@ -12121,11 +12129,11 @@
         <v>9</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D349" s="8"/>
       <c r="E349" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F349" s="9">
         <v>60</v>
@@ -12140,11 +12148,11 @@
         <v>6.98</v>
       </c>
       <c r="J349" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="350" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A350" s="8" t="s">
         <v>71</v>
       </c>
@@ -12152,11 +12160,11 @@
         <v>9</v>
       </c>
       <c r="C350" s="8" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D350" s="8"/>
       <c r="E350" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F350" s="9">
         <v>60</v>
@@ -12171,11 +12179,11 @@
         <v>17.21</v>
       </c>
       <c r="J350" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="351" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="6"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A351" s="8" t="s">
         <v>71</v>
       </c>
@@ -12187,7 +12195,7 @@
       </c>
       <c r="D351" s="8"/>
       <c r="E351" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F351" s="9">
         <v>60</v>
@@ -12202,11 +12210,11 @@
         <v>17.22</v>
       </c>
       <c r="J351" s="11" t="str">
-        <f t="shared" ref="J351:J380" si="6">"per" &amp; " " &amp;B351</f>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="352" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" ref="J351:J380" si="7">"per" &amp; " " &amp;B351</f>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A352" s="8" t="s">
         <v>71</v>
       </c>
@@ -12214,11 +12222,11 @@
         <v>9</v>
       </c>
       <c r="C352" s="8" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D352" s="8"/>
       <c r="E352" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F352" s="9">
         <v>60</v>
@@ -12233,11 +12241,11 @@
         <v>6.94</v>
       </c>
       <c r="J352" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="353" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A353" s="8" t="s">
         <v>71</v>
       </c>
@@ -12245,11 +12253,11 @@
         <v>9</v>
       </c>
       <c r="C353" s="8" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D353" s="8"/>
       <c r="E353" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F353" s="9">
         <v>60</v>
@@ -12264,11 +12272,11 @@
         <v>8.31</v>
       </c>
       <c r="J353" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="354" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A354" s="8" t="s">
         <v>71</v>
       </c>
@@ -12276,11 +12284,11 @@
         <v>9</v>
       </c>
       <c r="C354" s="8" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D354" s="8"/>
       <c r="E354" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F354" s="9">
         <v>60</v>
@@ -12295,11 +12303,11 @@
         <v>23.28</v>
       </c>
       <c r="J354" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="355" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A355" s="8" t="s">
         <v>71</v>
       </c>
@@ -12307,11 +12315,11 @@
         <v>9</v>
       </c>
       <c r="C355" s="8" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D355" s="8"/>
       <c r="E355" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F355" s="9">
         <v>60</v>
@@ -12326,11 +12334,11 @@
         <v>10.4</v>
       </c>
       <c r="J355" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="356" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A356" s="8" t="s">
         <v>71</v>
       </c>
@@ -12338,11 +12346,11 @@
         <v>9</v>
       </c>
       <c r="C356" s="8" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D356" s="8"/>
       <c r="E356" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F356" s="9">
         <v>60</v>
@@ -12357,11 +12365,11 @@
         <v>10.39</v>
       </c>
       <c r="J356" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="357" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A357" s="8" t="s">
         <v>71</v>
       </c>
@@ -12369,11 +12377,11 @@
         <v>9</v>
       </c>
       <c r="C357" s="8" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D357" s="8"/>
       <c r="E357" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F357" s="9">
         <v>60</v>
@@ -12388,11 +12396,11 @@
         <v>23.28</v>
       </c>
       <c r="J357" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="358" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A358" s="8" t="s">
         <v>71</v>
       </c>
@@ -12400,11 +12408,11 @@
         <v>9</v>
       </c>
       <c r="C358" s="8" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D358" s="8"/>
       <c r="E358" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F358" s="9">
         <v>60</v>
@@ -12419,11 +12427,11 @@
         <v>10.48</v>
       </c>
       <c r="J358" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="359" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A359" s="8" t="s">
         <v>71</v>
       </c>
@@ -12435,7 +12443,7 @@
       </c>
       <c r="D359" s="8"/>
       <c r="E359" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F359" s="9">
         <v>28</v>
@@ -12450,11 +12458,11 @@
         <v>10.7</v>
       </c>
       <c r="J359" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="360" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A360" s="8" t="s">
         <v>71</v>
       </c>
@@ -12462,11 +12470,11 @@
         <v>9</v>
       </c>
       <c r="C360" s="8" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D360" s="8"/>
       <c r="E360" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F360" s="9">
         <v>60</v>
@@ -12481,11 +12489,11 @@
         <v>25.82</v>
       </c>
       <c r="J360" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A361" s="8" t="s">
         <v>71</v>
       </c>
@@ -12497,7 +12505,7 @@
       </c>
       <c r="D361" s="8"/>
       <c r="E361" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F361" s="9">
         <v>60</v>
@@ -12512,11 +12520,11 @@
         <v>25.83</v>
       </c>
       <c r="J361" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A362" s="8" t="s">
         <v>71</v>
       </c>
@@ -12524,11 +12532,11 @@
         <v>9</v>
       </c>
       <c r="C362" s="8" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D362" s="8"/>
       <c r="E362" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F362" s="9">
         <v>30</v>
@@ -12543,11 +12551,11 @@
         <v>12.18</v>
       </c>
       <c r="J362" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A363" s="8" t="s">
         <v>71</v>
       </c>
@@ -12555,11 +12563,11 @@
         <v>9</v>
       </c>
       <c r="C363" s="8" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D363" s="8"/>
       <c r="E363" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F363" s="9">
         <v>60</v>
@@ -12574,11 +12582,11 @@
         <v>10.39</v>
       </c>
       <c r="J363" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A364" s="8" t="s">
         <v>71</v>
       </c>
@@ -12586,11 +12594,11 @@
         <v>9</v>
       </c>
       <c r="C364" s="8" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D364" s="8"/>
       <c r="E364" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F364" s="9">
         <v>60</v>
@@ -12605,11 +12613,11 @@
         <v>11.35</v>
       </c>
       <c r="J364" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A365" s="8" t="s">
         <v>71</v>
       </c>
@@ -12617,11 +12625,11 @@
         <v>9</v>
       </c>
       <c r="C365" s="8" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D365" s="8"/>
       <c r="E365" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F365" s="9">
         <v>60</v>
@@ -12636,11 +12644,11 @@
         <v>31.04</v>
       </c>
       <c r="J365" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A366" s="8" t="s">
         <v>71</v>
       </c>
@@ -12648,11 +12656,11 @@
         <v>9</v>
       </c>
       <c r="C366" s="8" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D366" s="8"/>
       <c r="E366" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F366" s="9">
         <v>60</v>
@@ -12667,11 +12675,11 @@
         <v>14.2</v>
       </c>
       <c r="J366" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A367" s="8" t="s">
         <v>71</v>
       </c>
@@ -12679,11 +12687,11 @@
         <v>9</v>
       </c>
       <c r="C367" s="8" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D367" s="8"/>
       <c r="E367" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F367" s="9">
         <v>60</v>
@@ -12698,11 +12706,11 @@
         <v>14.19</v>
       </c>
       <c r="J367" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A368" s="8" t="s">
         <v>71</v>
       </c>
@@ -12710,11 +12718,11 @@
         <v>9</v>
       </c>
       <c r="C368" s="8" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D368" s="8"/>
       <c r="E368" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F368" s="9">
         <v>60</v>
@@ -12729,11 +12737,11 @@
         <v>31.04</v>
       </c>
       <c r="J368" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A369" s="8" t="s">
         <v>71</v>
       </c>
@@ -12741,11 +12749,11 @@
         <v>9</v>
       </c>
       <c r="C369" s="8" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D369" s="8"/>
       <c r="E369" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F369" s="9">
         <v>30</v>
@@ -12760,11 +12768,11 @@
         <v>14.98</v>
       </c>
       <c r="J369" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A370" s="8" t="s">
         <v>71</v>
       </c>
@@ -12772,11 +12780,11 @@
         <v>9</v>
       </c>
       <c r="C370" s="8" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D370" s="8"/>
       <c r="E370" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F370" s="9">
         <v>60</v>
@@ -12791,11 +12799,11 @@
         <v>14.28</v>
       </c>
       <c r="J370" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A371" s="8" t="s">
         <v>71</v>
       </c>
@@ -12807,7 +12815,7 @@
       </c>
       <c r="D371" s="8"/>
       <c r="E371" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F371" s="9">
         <v>28</v>
@@ -12822,11 +12830,11 @@
         <v>14.26</v>
       </c>
       <c r="J371" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A372" s="8" t="s">
         <v>71</v>
       </c>
@@ -12834,11 +12842,11 @@
         <v>9</v>
       </c>
       <c r="C372" s="8" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D372" s="8"/>
       <c r="E372" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F372" s="9">
         <v>60</v>
@@ -12853,11 +12861,11 @@
         <v>34.43</v>
       </c>
       <c r="J372" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A373" s="8" t="s">
         <v>71</v>
       </c>
@@ -12869,7 +12877,7 @@
       </c>
       <c r="D373" s="8"/>
       <c r="E373" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F373" s="9">
         <v>60</v>
@@ -12884,11 +12892,11 @@
         <v>34.4</v>
       </c>
       <c r="J373" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A374" s="8" t="s">
         <v>71</v>
       </c>
@@ -12896,11 +12904,11 @@
         <v>9</v>
       </c>
       <c r="C374" s="8" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D374" s="8"/>
       <c r="E374" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F374" s="9">
         <v>30</v>
@@ -12915,11 +12923,11 @@
         <v>17.579999999999998</v>
       </c>
       <c r="J374" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A375" s="8" t="s">
         <v>71</v>
       </c>
@@ -12927,11 +12935,11 @@
         <v>9</v>
       </c>
       <c r="C375" s="8" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D375" s="8"/>
       <c r="E375" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F375" s="9">
         <v>60</v>
@@ -12946,11 +12954,11 @@
         <v>14.19</v>
       </c>
       <c r="J375" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A376" s="8" t="s">
         <v>71</v>
       </c>
@@ -12958,11 +12966,11 @@
         <v>9</v>
       </c>
       <c r="C376" s="8" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D376" s="8"/>
       <c r="E376" s="8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F376" s="9">
         <v>30</v>
@@ -12977,11 +12985,11 @@
         <v>22.47</v>
       </c>
       <c r="J376" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A377" s="8" t="s">
         <v>71</v>
       </c>
@@ -12993,7 +13001,7 @@
       </c>
       <c r="D377" s="8"/>
       <c r="E377" s="8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F377" s="9">
         <v>28</v>
@@ -13008,11 +13016,11 @@
         <v>21.39</v>
       </c>
       <c r="J377" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="378" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A378" s="8" t="s">
         <v>71</v>
       </c>
@@ -13020,11 +13028,11 @@
         <v>9</v>
       </c>
       <c r="C378" s="8" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D378" s="8"/>
       <c r="E378" s="8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F378" s="9">
         <v>30</v>
@@ -13039,11 +13047,11 @@
         <v>24.94</v>
       </c>
       <c r="J378" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A379" s="8" t="s">
         <v>71</v>
       </c>
@@ -13055,7 +13063,7 @@
       </c>
       <c r="D379" s="8"/>
       <c r="E379" s="8" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F379" s="9">
         <v>28</v>
@@ -13070,11 +13078,11 @@
         <v>28.51</v>
       </c>
       <c r="J379" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A380" s="8" t="s">
         <v>71</v>
       </c>
@@ -13082,11 +13090,11 @@
         <v>9</v>
       </c>
       <c r="C380" s="8" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D380" s="8"/>
       <c r="E380" s="8" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F380" s="9">
         <v>30</v>
@@ -13101,11 +13109,11 @@
         <v>32.47</v>
       </c>
       <c r="J380" s="11" t="str">
-        <f t="shared" si="6"/>
-        <v>per Tablet</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" ht="22.5" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>per Tablet</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A381" s="3"/>
       <c r="B381" s="4"/>
       <c r="C381" s="3"/>
@@ -13116,7 +13124,7 @@
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
     </row>
-    <row r="382" spans="1:10" ht="22.5" customHeight="1">
+    <row r="382" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A382" s="3"/>
       <c r="B382" s="4"/>
       <c r="C382" s="3"/>
@@ -13127,7 +13135,7 @@
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
     </row>
-    <row r="383" spans="1:10" ht="22.5" customHeight="1">
+    <row r="383" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A383" s="3"/>
       <c r="B383" s="4"/>
       <c r="C383" s="3"/>
@@ -13138,7 +13146,7 @@
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
     </row>
-    <row r="384" spans="1:10" ht="22.5" customHeight="1">
+    <row r="384" spans="1:10" ht="22.5" hidden="1" customHeight="1">
       <c r="A384" s="3"/>
       <c r="B384" s="4"/>
       <c r="C384" s="3"/>
@@ -13149,7 +13157,7 @@
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
     </row>
-    <row r="385" spans="1:9" ht="22.5" customHeight="1">
+    <row r="385" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A385" s="3"/>
       <c r="B385" s="4"/>
       <c r="C385" s="3"/>
@@ -13160,7 +13168,7 @@
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
     </row>
-    <row r="386" spans="1:9" ht="22.5" customHeight="1">
+    <row r="386" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A386" s="3"/>
       <c r="B386" s="4"/>
       <c r="C386" s="3"/>
@@ -13171,7 +13179,7 @@
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
     </row>
-    <row r="387" spans="1:9" ht="22.5" customHeight="1">
+    <row r="387" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A387" s="3"/>
       <c r="B387" s="4"/>
       <c r="C387" s="3"/>
@@ -13182,7 +13190,7 @@
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
     </row>
-    <row r="388" spans="1:9" ht="22.5" customHeight="1">
+    <row r="388" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A388" s="3"/>
       <c r="B388" s="4"/>
       <c r="C388" s="3"/>
@@ -13193,7 +13201,7 @@
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
     </row>
-    <row r="389" spans="1:9" ht="22.5" customHeight="1">
+    <row r="389" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A389" s="3"/>
       <c r="B389" s="4"/>
       <c r="C389" s="3"/>
@@ -13204,7 +13212,7 @@
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
     </row>
-    <row r="390" spans="1:9" ht="22.5" customHeight="1">
+    <row r="390" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A390" s="3"/>
       <c r="B390" s="4"/>
       <c r="C390" s="3"/>
@@ -13215,7 +13223,7 @@
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
     </row>
-    <row r="391" spans="1:9" ht="22.5" customHeight="1">
+    <row r="391" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A391" s="3"/>
       <c r="B391" s="4"/>
       <c r="C391" s="3"/>
@@ -13226,7 +13234,7 @@
       <c r="H391" s="4"/>
       <c r="I391" s="4"/>
     </row>
-    <row r="392" spans="1:9" ht="22.5" customHeight="1">
+    <row r="392" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A392" s="3"/>
       <c r="B392" s="4"/>
       <c r="C392" s="3"/>
@@ -13237,7 +13245,7 @@
       <c r="H392" s="4"/>
       <c r="I392" s="4"/>
     </row>
-    <row r="393" spans="1:9" ht="22.5" customHeight="1">
+    <row r="393" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A393" s="3"/>
       <c r="B393" s="4"/>
       <c r="C393" s="3"/>
@@ -13248,7 +13256,7 @@
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
     </row>
-    <row r="394" spans="1:9" ht="22.5" customHeight="1">
+    <row r="394" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A394" s="3"/>
       <c r="B394" s="4"/>
       <c r="C394" s="3"/>
@@ -13259,7 +13267,7 @@
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
     </row>
-    <row r="395" spans="1:9" ht="22.5" customHeight="1">
+    <row r="395" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A395" s="3"/>
       <c r="B395" s="4"/>
       <c r="C395" s="3"/>
@@ -13270,7 +13278,7 @@
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
     </row>
-    <row r="396" spans="1:9" ht="22.5" customHeight="1">
+    <row r="396" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A396" s="3"/>
       <c r="B396" s="4"/>
       <c r="C396" s="3"/>
@@ -13281,7 +13289,7 @@
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
     </row>
-    <row r="397" spans="1:9" ht="22.5" customHeight="1">
+    <row r="397" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A397" s="3"/>
       <c r="B397" s="4"/>
       <c r="C397" s="3"/>
@@ -13292,7 +13300,7 @@
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
     </row>
-    <row r="398" spans="1:9" ht="22.5" customHeight="1">
+    <row r="398" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A398" s="3"/>
       <c r="B398" s="4"/>
       <c r="C398" s="3"/>
@@ -13303,7 +13311,7 @@
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
     </row>
-    <row r="399" spans="1:9" ht="22.5" customHeight="1">
+    <row r="399" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A399" s="3"/>
       <c r="B399" s="4"/>
       <c r="C399" s="3"/>
@@ -13314,7 +13322,7 @@
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
     </row>
-    <row r="400" spans="1:9" ht="22.5" customHeight="1">
+    <row r="400" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A400" s="3"/>
       <c r="B400" s="4"/>
       <c r="C400" s="3"/>
@@ -13325,7 +13333,7 @@
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
     </row>
-    <row r="401" spans="1:9" ht="22.5" customHeight="1">
+    <row r="401" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A401" s="3"/>
       <c r="B401" s="4"/>
       <c r="C401" s="3"/>
@@ -13336,7 +13344,7 @@
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
     </row>
-    <row r="402" spans="1:9" ht="22.5" customHeight="1">
+    <row r="402" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A402" s="3"/>
       <c r="B402" s="4"/>
       <c r="C402" s="3"/>
@@ -13347,7 +13355,7 @@
       <c r="H402" s="4"/>
       <c r="I402" s="4"/>
     </row>
-    <row r="403" spans="1:9" ht="22.5" customHeight="1">
+    <row r="403" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A403" s="3"/>
       <c r="B403" s="4"/>
       <c r="C403" s="3"/>
@@ -13358,7 +13366,7 @@
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
     </row>
-    <row r="404" spans="1:9" ht="22.5" customHeight="1">
+    <row r="404" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A404" s="3"/>
       <c r="B404" s="4"/>
       <c r="C404" s="3"/>
@@ -13369,7 +13377,7 @@
       <c r="H404" s="4"/>
       <c r="I404" s="4"/>
     </row>
-    <row r="405" spans="1:9" ht="22.5" customHeight="1">
+    <row r="405" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A405" s="3"/>
       <c r="B405" s="4"/>
       <c r="C405" s="3"/>
@@ -13380,7 +13388,7 @@
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
     </row>
-    <row r="406" spans="1:9" ht="22.5" customHeight="1">
+    <row r="406" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A406" s="3"/>
       <c r="B406" s="4"/>
       <c r="C406" s="3"/>
@@ -13391,7 +13399,7 @@
       <c r="H406" s="4"/>
       <c r="I406" s="4"/>
     </row>
-    <row r="407" spans="1:9" ht="22.5" customHeight="1">
+    <row r="407" spans="1:9" ht="22.5" hidden="1" customHeight="1">
       <c r="A407" s="3"/>
       <c r="B407" s="4"/>
       <c r="C407" s="3"/>
@@ -13403,6 +13411,21 @@
       <c r="I407" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B407" xr:uid="{537DEBE9-B305-49C6-BA8B-E5C9DA8CC8BE}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Buprenorphine"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Tablet"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A200:J224">
+    <sortCondition ref="C2:C407"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inst/extdata/medicaton_costs_all.xlsx
+++ b/inst/extdata/medicaton_costs_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sheej\Documents\Sheeja_WinLap\repos\packDAMipd\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D31BC17C-1180-49AB-B822-8CF32AF217B0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F4F3D9-2476-4853-BFBE-90FB610EF142}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$407</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1164,7 +1163,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J407"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1210,7 +1208,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="2" spans="1:10" ht="22.5" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
@@ -1241,7 +1239,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="3" spans="1:10" ht="22.5" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
@@ -1272,7 +1270,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="4" spans="1:10" ht="22.5" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -1303,7 +1301,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:10" ht="22.5" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
@@ -1334,7 +1332,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="6" spans="1:10" ht="22.5" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -1365,7 +1363,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="7" spans="1:10" ht="22.5" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
@@ -1396,7 +1394,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="8" spans="1:10" ht="22.5" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>15</v>
       </c>
@@ -1429,7 +1427,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="9" spans="1:10" ht="22.5" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>20</v>
       </c>
@@ -1462,7 +1460,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:10" ht="22.5" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
@@ -1495,7 +1493,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="11" spans="1:10" ht="22.5" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>27</v>
       </c>
@@ -1528,7 +1526,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="12" spans="1:10" ht="22.5" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
@@ -1561,7 +1559,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="13" spans="1:10" ht="22.5" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>27</v>
       </c>
@@ -1594,7 +1592,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:10" ht="22.5" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>32</v>
       </c>
@@ -1627,7 +1625,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="15" spans="1:10" ht="22.5" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>35</v>
       </c>
@@ -1660,7 +1658,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="16" spans="1:10" ht="22.5" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>39</v>
       </c>
@@ -1693,7 +1691,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="17" spans="1:10" ht="22.5" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>39</v>
       </c>
@@ -1726,7 +1724,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="18" spans="1:10" ht="22.5" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
@@ -1759,7 +1757,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="19" spans="1:10" ht="22.5" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>39</v>
       </c>
@@ -1792,7 +1790,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="20" spans="1:10" ht="22.5" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>39</v>
       </c>
@@ -1825,7 +1823,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="21" spans="1:10" ht="22.5" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>39</v>
       </c>
@@ -1858,7 +1856,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="22" spans="1:10" ht="22.5" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>39</v>
       </c>
@@ -1891,7 +1889,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="23" spans="1:10" ht="22.5" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>39</v>
       </c>
@@ -1924,7 +1922,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="24" spans="1:10" ht="22.5" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>39</v>
       </c>
@@ -1957,7 +1955,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="25" spans="1:10" ht="22.5" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>50</v>
       </c>
@@ -1990,7 +1988,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="26" spans="1:10" ht="22.5" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>50</v>
       </c>
@@ -2023,7 +2021,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="27" spans="1:10" ht="22.5" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>50</v>
       </c>
@@ -2056,7 +2054,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="28" spans="1:10" ht="22.5" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>50</v>
       </c>
@@ -2089,7 +2087,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="29" spans="1:10" ht="22.5" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>50</v>
       </c>
@@ -2122,7 +2120,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="30" spans="1:10" ht="22.5" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>50</v>
       </c>
@@ -2155,7 +2153,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="31" spans="1:10" ht="22.5" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>50</v>
       </c>
@@ -2188,7 +2186,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="32" spans="1:10" ht="22.5" customHeight="1">
       <c r="A32" s="8" t="s">
         <v>50</v>
       </c>
@@ -2221,7 +2219,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="33" spans="1:10" ht="22.5" customHeight="1">
       <c r="A33" s="8" t="s">
         <v>50</v>
       </c>
@@ -2254,7 +2252,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="34" spans="1:10" ht="22.5" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>50</v>
       </c>
@@ -2287,7 +2285,7 @@
         <v>per Vial</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="35" spans="1:10" ht="22.5" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>50</v>
       </c>
@@ -2320,7 +2318,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="36" spans="1:10" ht="22.5" customHeight="1">
       <c r="A36" s="8" t="s">
         <v>50</v>
       </c>
@@ -2353,7 +2351,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="37" spans="1:10" ht="22.5" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>66</v>
       </c>
@@ -2386,7 +2384,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="38" spans="1:10" ht="22.5" customHeight="1">
       <c r="A38" s="8" t="s">
         <v>66</v>
       </c>
@@ -2419,7 +2417,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="39" spans="1:10" ht="22.5" customHeight="1">
       <c r="A39" s="8" t="s">
         <v>66</v>
       </c>
@@ -2452,7 +2450,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="40" spans="1:10" ht="22.5" customHeight="1">
       <c r="A40" s="8" t="s">
         <v>66</v>
       </c>
@@ -2485,7 +2483,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="41" spans="1:10" ht="22.5" customHeight="1">
       <c r="A41" s="8" t="s">
         <v>66</v>
       </c>
@@ -2518,7 +2516,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="42" spans="1:10" ht="22.5" customHeight="1">
       <c r="A42" s="8" t="s">
         <v>66</v>
       </c>
@@ -2551,7 +2549,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="43" spans="1:10" ht="22.5" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>66</v>
       </c>
@@ -2584,7 +2582,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="44" spans="1:10" ht="22.5" customHeight="1">
       <c r="A44" s="8" t="s">
         <v>66</v>
       </c>
@@ -2617,7 +2615,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="45" spans="1:10" ht="22.5" customHeight="1">
       <c r="A45" s="8" t="s">
         <v>66</v>
       </c>
@@ -2650,7 +2648,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="46" spans="1:10" ht="22.5" customHeight="1">
       <c r="A46" s="8" t="s">
         <v>66</v>
       </c>
@@ -2683,7 +2681,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="47" spans="1:10" ht="22.5" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>66</v>
       </c>
@@ -2716,7 +2714,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="48" spans="1:10" ht="22.5" customHeight="1">
       <c r="A48" s="8" t="s">
         <v>66</v>
       </c>
@@ -2749,7 +2747,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="49" spans="1:10" ht="22.5" customHeight="1">
       <c r="A49" s="8" t="s">
         <v>69</v>
       </c>
@@ -2782,7 +2780,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="50" spans="1:10" ht="22.5" customHeight="1">
       <c r="A50" s="8" t="s">
         <v>69</v>
       </c>
@@ -2815,7 +2813,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="51" spans="1:10" ht="22.5" customHeight="1">
       <c r="A51" s="8" t="s">
         <v>69</v>
       </c>
@@ -2848,7 +2846,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="52" spans="1:10" ht="22.5" customHeight="1">
       <c r="A52" s="8" t="s">
         <v>71</v>
       </c>
@@ -2881,7 +2879,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="53" spans="1:10" ht="22.5" customHeight="1">
       <c r="A53" s="8" t="s">
         <v>71</v>
       </c>
@@ -2914,7 +2912,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="54" spans="1:10" ht="22.5" customHeight="1">
       <c r="A54" s="8" t="s">
         <v>71</v>
       </c>
@@ -2947,7 +2945,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="55" spans="1:10" ht="22.5" customHeight="1">
       <c r="A55" s="8" t="s">
         <v>71</v>
       </c>
@@ -2980,7 +2978,7 @@
         <v>per Ampoule</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="56" spans="1:10" ht="22.5" customHeight="1">
       <c r="A56" s="8" t="s">
         <v>20</v>
       </c>
@@ -3013,7 +3011,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="57" spans="1:10" ht="22.5" customHeight="1">
       <c r="A57" s="8" t="s">
         <v>20</v>
       </c>
@@ -3046,7 +3044,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="58" spans="1:10" ht="22.5" customHeight="1">
       <c r="A58" s="8" t="s">
         <v>20</v>
       </c>
@@ -3079,7 +3077,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="59" spans="1:10" ht="22.5" customHeight="1">
       <c r="A59" s="8" t="s">
         <v>20</v>
       </c>
@@ -3112,7 +3110,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="60" spans="1:10" ht="22.5" customHeight="1">
       <c r="A60" s="8" t="s">
         <v>20</v>
       </c>
@@ -3145,7 +3143,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="61" spans="1:10" ht="22.5" customHeight="1">
       <c r="A61" s="8" t="s">
         <v>23</v>
       </c>
@@ -3178,7 +3176,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="62" spans="1:10" ht="22.5" customHeight="1">
       <c r="A62" s="8" t="s">
         <v>82</v>
       </c>
@@ -3211,7 +3209,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="63" spans="1:10" ht="22.5" customHeight="1">
       <c r="A63" s="8" t="s">
         <v>82</v>
       </c>
@@ -3244,7 +3242,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="64" spans="1:10" ht="22.5" customHeight="1">
       <c r="A64" s="8" t="s">
         <v>82</v>
       </c>
@@ -3277,7 +3275,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="65" spans="1:10" ht="22.5" customHeight="1">
       <c r="A65" s="8" t="s">
         <v>82</v>
       </c>
@@ -3310,7 +3308,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="66" spans="1:10" ht="22.5" customHeight="1">
       <c r="A66" s="8" t="s">
         <v>82</v>
       </c>
@@ -3343,7 +3341,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="67" spans="1:10" ht="22.5" customHeight="1">
       <c r="A67" s="8" t="s">
         <v>82</v>
       </c>
@@ -3376,7 +3374,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="68" spans="1:10" ht="22.5" customHeight="1">
       <c r="A68" s="8" t="s">
         <v>82</v>
       </c>
@@ -3409,7 +3407,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="69" spans="1:10" ht="22.5" customHeight="1">
       <c r="A69" s="8" t="s">
         <v>82</v>
       </c>
@@ -3442,7 +3440,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="70" spans="1:10" ht="22.5" customHeight="1">
       <c r="A70" s="8" t="s">
         <v>82</v>
       </c>
@@ -3475,7 +3473,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="71" spans="1:10" ht="22.5" customHeight="1">
       <c r="A71" s="8" t="s">
         <v>82</v>
       </c>
@@ -3508,7 +3506,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="72" spans="1:10" ht="22.5" customHeight="1">
       <c r="A72" s="8" t="s">
         <v>82</v>
       </c>
@@ -3541,7 +3539,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="73" spans="1:10" ht="22.5" customHeight="1">
       <c r="A73" s="8" t="s">
         <v>82</v>
       </c>
@@ -3574,7 +3572,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="74" spans="1:10" ht="22.5" customHeight="1">
       <c r="A74" s="8" t="s">
         <v>82</v>
       </c>
@@ -3607,7 +3605,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="75" spans="1:10" ht="22.5" customHeight="1">
       <c r="A75" s="8" t="s">
         <v>82</v>
       </c>
@@ -3640,7 +3638,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="76" spans="1:10" ht="22.5" customHeight="1">
       <c r="A76" s="8" t="s">
         <v>82</v>
       </c>
@@ -3673,7 +3671,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="77" spans="1:10" ht="22.5" customHeight="1">
       <c r="A77" s="8" t="s">
         <v>82</v>
       </c>
@@ -3706,7 +3704,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="78" spans="1:10" ht="22.5" customHeight="1">
       <c r="A78" s="8" t="s">
         <v>50</v>
       </c>
@@ -3739,7 +3737,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="79" spans="1:10" ht="22.5" customHeight="1">
       <c r="A79" s="8" t="s">
         <v>50</v>
       </c>
@@ -3772,7 +3770,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="80" spans="1:10" ht="22.5" customHeight="1">
       <c r="A80" s="8" t="s">
         <v>50</v>
       </c>
@@ -3805,7 +3803,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="81" spans="1:10" ht="22.5" customHeight="1">
       <c r="A81" s="8" t="s">
         <v>50</v>
       </c>
@@ -3838,7 +3836,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="82" spans="1:10" ht="22.5" customHeight="1">
       <c r="A82" s="8" t="s">
         <v>50</v>
       </c>
@@ -3871,7 +3869,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="83" spans="1:10" ht="22.5" customHeight="1">
       <c r="A83" s="8" t="s">
         <v>50</v>
       </c>
@@ -3904,7 +3902,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="84" spans="1:10" ht="22.5" customHeight="1">
       <c r="A84" s="8" t="s">
         <v>50</v>
       </c>
@@ -3937,7 +3935,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="85" spans="1:10" ht="22.5" customHeight="1">
       <c r="A85" s="8" t="s">
         <v>50</v>
       </c>
@@ -3970,7 +3968,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="86" spans="1:10" ht="22.5" customHeight="1">
       <c r="A86" s="8" t="s">
         <v>66</v>
       </c>
@@ -4003,7 +4001,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="87" spans="1:10" ht="22.5" customHeight="1">
       <c r="A87" s="8" t="s">
         <v>66</v>
       </c>
@@ -4036,7 +4034,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="88" spans="1:10" ht="22.5" customHeight="1">
       <c r="A88" s="8" t="s">
         <v>66</v>
       </c>
@@ -4069,7 +4067,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="89" spans="1:10" ht="22.5" customHeight="1">
       <c r="A89" s="8" t="s">
         <v>66</v>
       </c>
@@ -4102,7 +4100,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="90" spans="1:10" ht="22.5" customHeight="1">
       <c r="A90" s="8" t="s">
         <v>66</v>
       </c>
@@ -4135,7 +4133,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="91" spans="1:10" ht="22.5" customHeight="1">
       <c r="A91" s="8" t="s">
         <v>66</v>
       </c>
@@ -4168,7 +4166,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="92" spans="1:10" ht="22.5" customHeight="1">
       <c r="A92" s="8" t="s">
         <v>88</v>
       </c>
@@ -4201,7 +4199,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="93" spans="1:10" ht="22.5" customHeight="1">
       <c r="A93" s="8" t="s">
         <v>88</v>
       </c>
@@ -4234,7 +4232,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="94" spans="1:10" ht="22.5" customHeight="1">
       <c r="A94" s="8" t="s">
         <v>71</v>
       </c>
@@ -4267,7 +4265,7 @@
         <v>per Bottle</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="95" spans="1:10" ht="22.5" customHeight="1">
       <c r="A95" s="8" t="s">
         <v>15</v>
       </c>
@@ -4298,7 +4296,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="96" spans="1:10" ht="22.5" customHeight="1">
       <c r="A96" s="8" t="s">
         <v>15</v>
       </c>
@@ -4329,7 +4327,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="97" spans="1:10" ht="22.5" customHeight="1">
       <c r="A97" s="8" t="s">
         <v>15</v>
       </c>
@@ -4360,7 +4358,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="98" spans="1:10" ht="22.5" customHeight="1">
       <c r="A98" s="8" t="s">
         <v>15</v>
       </c>
@@ -4391,7 +4389,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="99" spans="1:10" ht="22.5" customHeight="1">
       <c r="A99" s="8" t="s">
         <v>15</v>
       </c>
@@ -4422,7 +4420,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="100" spans="1:10" ht="22.5" customHeight="1">
       <c r="A100" s="8" t="s">
         <v>15</v>
       </c>
@@ -4453,7 +4451,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="101" spans="1:10" ht="22.5" customHeight="1">
       <c r="A101" s="8" t="s">
         <v>15</v>
       </c>
@@ -4484,7 +4482,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="102" spans="1:10" ht="22.5" customHeight="1">
       <c r="A102" s="8" t="s">
         <v>15</v>
       </c>
@@ -4515,7 +4513,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="103" spans="1:10" ht="22.5" customHeight="1">
       <c r="A103" s="8" t="s">
         <v>15</v>
       </c>
@@ -4546,7 +4544,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="104" spans="1:10" ht="22.5" customHeight="1">
       <c r="A104" s="8" t="s">
         <v>15</v>
       </c>
@@ -4577,7 +4575,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="105" spans="1:10" ht="22.5" customHeight="1">
       <c r="A105" s="8" t="s">
         <v>15</v>
       </c>
@@ -4608,7 +4606,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="106" spans="1:10" ht="22.5" customHeight="1">
       <c r="A106" s="8" t="s">
         <v>15</v>
       </c>
@@ -4639,7 +4637,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="107" spans="1:10" ht="22.5" customHeight="1">
       <c r="A107" s="8" t="s">
         <v>15</v>
       </c>
@@ -4670,7 +4668,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="108" spans="1:10" ht="22.5" customHeight="1">
       <c r="A108" s="8" t="s">
         <v>15</v>
       </c>
@@ -4701,7 +4699,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="109" spans="1:10" ht="22.5" customHeight="1">
       <c r="A109" s="8" t="s">
         <v>15</v>
       </c>
@@ -4732,7 +4730,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="110" spans="1:10" ht="22.5" customHeight="1">
       <c r="A110" s="8" t="s">
         <v>15</v>
       </c>
@@ -4763,7 +4761,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="111" spans="1:10" ht="22.5" customHeight="1">
       <c r="A111" s="8" t="s">
         <v>15</v>
       </c>
@@ -4794,7 +4792,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="112" spans="1:10" ht="22.5" customHeight="1">
       <c r="A112" s="8" t="s">
         <v>15</v>
       </c>
@@ -4825,7 +4823,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="113" spans="1:10" ht="22.5" customHeight="1">
       <c r="A113" s="8" t="s">
         <v>15</v>
       </c>
@@ -4856,7 +4854,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="114" spans="1:10" ht="22.5" customHeight="1">
       <c r="A114" s="8" t="s">
         <v>15</v>
       </c>
@@ -4887,7 +4885,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="115" spans="1:10" ht="22.5" customHeight="1">
       <c r="A115" s="8" t="s">
         <v>15</v>
       </c>
@@ -4918,7 +4916,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="116" spans="1:10" ht="22.5" customHeight="1">
       <c r="A116" s="8" t="s">
         <v>15</v>
       </c>
@@ -4949,7 +4947,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="117" spans="1:10" ht="22.5" customHeight="1">
       <c r="A117" s="8" t="s">
         <v>15</v>
       </c>
@@ -4980,7 +4978,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="118" spans="1:10" ht="22.5" customHeight="1">
       <c r="A118" s="8" t="s">
         <v>15</v>
       </c>
@@ -5011,7 +5009,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="119" spans="1:10" ht="22.5" customHeight="1">
       <c r="A119" s="8" t="s">
         <v>15</v>
       </c>
@@ -5042,7 +5040,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="120" spans="1:10" ht="22.5" customHeight="1">
       <c r="A120" s="8" t="s">
         <v>15</v>
       </c>
@@ -5073,7 +5071,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="121" spans="1:10" ht="22.5" customHeight="1">
       <c r="A121" s="8" t="s">
         <v>15</v>
       </c>
@@ -5104,7 +5102,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="122" spans="1:10" ht="22.5" customHeight="1">
       <c r="A122" s="8" t="s">
         <v>15</v>
       </c>
@@ -5135,7 +5133,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="123" spans="1:10" ht="22.5" customHeight="1">
       <c r="A123" s="8" t="s">
         <v>15</v>
       </c>
@@ -5166,7 +5164,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="124" spans="1:10" ht="22.5" customHeight="1">
       <c r="A124" s="8" t="s">
         <v>15</v>
       </c>
@@ -5197,7 +5195,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="125" spans="1:10" ht="22.5" customHeight="1">
       <c r="A125" s="8" t="s">
         <v>15</v>
       </c>
@@ -5228,7 +5226,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="126" spans="1:10" ht="22.5" customHeight="1">
       <c r="A126" s="8" t="s">
         <v>15</v>
       </c>
@@ -5259,7 +5257,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="127" spans="1:10" ht="22.5" customHeight="1">
       <c r="A127" s="8" t="s">
         <v>15</v>
       </c>
@@ -5290,7 +5288,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="128" spans="1:10" ht="22.5" customHeight="1">
       <c r="A128" s="8" t="s">
         <v>15</v>
       </c>
@@ -5321,7 +5319,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="129" spans="1:10" ht="22.5" customHeight="1">
       <c r="A129" s="8" t="s">
         <v>15</v>
       </c>
@@ -5352,7 +5350,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="130" spans="1:10" ht="22.5" customHeight="1">
       <c r="A130" s="8" t="s">
         <v>15</v>
       </c>
@@ -5383,7 +5381,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="131" spans="1:10" ht="22.5" customHeight="1">
       <c r="A131" s="8" t="s">
         <v>27</v>
       </c>
@@ -5414,7 +5412,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="132" spans="1:10" ht="22.5" customHeight="1">
       <c r="A132" s="8" t="s">
         <v>27</v>
       </c>
@@ -5445,7 +5443,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="133" spans="1:10" ht="22.5" customHeight="1">
       <c r="A133" s="8" t="s">
         <v>27</v>
       </c>
@@ -5476,7 +5474,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="134" spans="1:10" ht="22.5" customHeight="1">
       <c r="A134" s="8" t="s">
         <v>27</v>
       </c>
@@ -5507,7 +5505,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="135" spans="1:10" ht="22.5" customHeight="1">
       <c r="A135" s="8" t="s">
         <v>27</v>
       </c>
@@ -5538,7 +5536,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="136" spans="1:10" ht="22.5" customHeight="1">
       <c r="A136" s="8" t="s">
         <v>27</v>
       </c>
@@ -5569,7 +5567,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="137" spans="1:10" ht="22.5" customHeight="1">
       <c r="A137" s="8" t="s">
         <v>27</v>
       </c>
@@ -5598,7 +5596,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="138" spans="1:10" ht="22.5" customHeight="1">
       <c r="A138" s="8" t="s">
         <v>27</v>
       </c>
@@ -5627,7 +5625,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="139" spans="1:10" ht="22.5" customHeight="1">
       <c r="A139" s="8" t="s">
         <v>27</v>
       </c>
@@ -5658,7 +5656,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="140" spans="1:10" ht="22.5" customHeight="1">
       <c r="A140" s="8" t="s">
         <v>27</v>
       </c>
@@ -5689,7 +5687,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="141" spans="1:10" ht="22.5" customHeight="1">
       <c r="A141" s="8" t="s">
         <v>27</v>
       </c>
@@ -5720,7 +5718,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="142" spans="1:10" ht="22.5" customHeight="1">
       <c r="A142" s="8" t="s">
         <v>27</v>
       </c>
@@ -5751,7 +5749,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="143" spans="1:10" ht="22.5" customHeight="1">
       <c r="A143" s="8" t="s">
         <v>27</v>
       </c>
@@ -5782,7 +5780,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="144" spans="1:10" ht="22.5" customHeight="1">
       <c r="A144" s="8" t="s">
         <v>27</v>
       </c>
@@ -5813,7 +5811,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="145" spans="1:10" ht="22.5" customHeight="1">
       <c r="A145" s="8" t="s">
         <v>27</v>
       </c>
@@ -5844,7 +5842,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="146" spans="1:10" ht="22.5" customHeight="1">
       <c r="A146" s="8" t="s">
         <v>27</v>
       </c>
@@ -5873,7 +5871,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="147" spans="1:10" ht="22.5" customHeight="1">
       <c r="A147" s="8" t="s">
         <v>27</v>
       </c>
@@ -5902,7 +5900,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="148" spans="1:10" ht="22.5" customHeight="1">
       <c r="A148" s="8" t="s">
         <v>27</v>
       </c>
@@ -5933,7 +5931,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="149" spans="1:10" ht="22.5" customHeight="1">
       <c r="A149" s="8" t="s">
         <v>27</v>
       </c>
@@ -5964,7 +5962,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="150" spans="1:10" ht="22.5" customHeight="1">
       <c r="A150" s="8" t="s">
         <v>27</v>
       </c>
@@ -5995,7 +5993,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="151" spans="1:10" ht="22.5" customHeight="1">
       <c r="A151" s="8" t="s">
         <v>27</v>
       </c>
@@ -6026,7 +6024,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="152" spans="1:10" ht="22.5" customHeight="1">
       <c r="A152" s="8" t="s">
         <v>27</v>
       </c>
@@ -6057,7 +6055,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="153" spans="1:10" ht="22.5" customHeight="1">
       <c r="A153" s="8" t="s">
         <v>27</v>
       </c>
@@ -6088,7 +6086,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="154" spans="1:10" ht="22.5" customHeight="1">
       <c r="A154" s="8" t="s">
         <v>27</v>
       </c>
@@ -6119,7 +6117,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="155" spans="1:10" ht="22.5" customHeight="1">
       <c r="A155" s="8" t="s">
         <v>27</v>
       </c>
@@ -6148,7 +6146,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="156" spans="1:10" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
         <v>27</v>
       </c>
@@ -6177,7 +6175,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="157" spans="1:10" ht="22.5" customHeight="1">
       <c r="A157" s="8" t="s">
         <v>27</v>
       </c>
@@ -6206,7 +6204,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="158" spans="1:10" ht="22.5" customHeight="1">
       <c r="A158" s="8" t="s">
         <v>27</v>
       </c>
@@ -6237,7 +6235,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="159" spans="1:10" ht="22.5" customHeight="1">
       <c r="A159" s="8" t="s">
         <v>27</v>
       </c>
@@ -6268,7 +6266,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="160" spans="1:10" ht="22.5" customHeight="1">
       <c r="A160" s="8" t="s">
         <v>27</v>
       </c>
@@ -6299,7 +6297,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="161" spans="1:10" ht="22.5" customHeight="1">
       <c r="A161" s="8" t="s">
         <v>27</v>
       </c>
@@ -6330,7 +6328,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="162" spans="1:10" ht="22.5" customHeight="1">
       <c r="A162" s="8" t="s">
         <v>27</v>
       </c>
@@ -6361,7 +6359,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="163" spans="1:10" ht="22.5" customHeight="1">
       <c r="A163" s="8" t="s">
         <v>27</v>
       </c>
@@ -6392,7 +6390,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="164" spans="1:10" ht="22.5" customHeight="1">
       <c r="A164" s="8" t="s">
         <v>27</v>
       </c>
@@ -6421,7 +6419,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="165" spans="1:10" ht="22.5" customHeight="1">
       <c r="A165" s="8" t="s">
         <v>27</v>
       </c>
@@ -6450,7 +6448,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="166" spans="1:10" ht="22.5" customHeight="1">
       <c r="A166" s="8" t="s">
         <v>27</v>
       </c>
@@ -6479,7 +6477,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="39" hidden="1" customHeight="1">
+    <row r="167" spans="1:10" ht="39" customHeight="1">
       <c r="A167" s="8" t="s">
         <v>27</v>
       </c>
@@ -6510,7 +6508,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="168" spans="1:10" ht="22.5" customHeight="1">
       <c r="A168" s="8" t="s">
         <v>27</v>
       </c>
@@ -6541,7 +6539,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="169" spans="1:10" ht="22.5" customHeight="1">
       <c r="A169" s="8" t="s">
         <v>27</v>
       </c>
@@ -6572,7 +6570,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="170" spans="1:10" ht="22.5" customHeight="1">
       <c r="A170" s="8" t="s">
         <v>27</v>
       </c>
@@ -6603,7 +6601,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="171" spans="1:10" ht="22.5" customHeight="1">
       <c r="A171" s="8" t="s">
         <v>27</v>
       </c>
@@ -6634,7 +6632,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="172" spans="1:10" ht="22.5" customHeight="1">
       <c r="A172" s="8" t="s">
         <v>27</v>
       </c>
@@ -6665,7 +6663,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="173" spans="1:10" ht="22.5" customHeight="1">
       <c r="A173" s="8" t="s">
         <v>27</v>
       </c>
@@ -6696,7 +6694,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="174" spans="1:10" ht="22.5" customHeight="1">
       <c r="A174" s="8" t="s">
         <v>27</v>
       </c>
@@ -6727,7 +6725,7 @@
         <v>per Patch</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="175" spans="1:10" ht="22.5" customHeight="1">
       <c r="A175" s="8" t="s">
         <v>27</v>
       </c>
@@ -7347,7 +7345,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="195" spans="1:10" ht="22.5" customHeight="1">
       <c r="A195" s="8" t="s">
         <v>141</v>
       </c>
@@ -7378,7 +7376,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="196" spans="1:10" ht="22.5" customHeight="1">
       <c r="A196" s="8" t="s">
         <v>141</v>
       </c>
@@ -7409,7 +7407,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="197" spans="1:10" ht="22.5" customHeight="1">
       <c r="A197" s="8" t="s">
         <v>141</v>
       </c>
@@ -7440,7 +7438,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="198" spans="1:10" ht="22.5" customHeight="1">
       <c r="A198" s="8" t="s">
         <v>141</v>
       </c>
@@ -7471,7 +7469,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="199" spans="1:10" ht="22.5" customHeight="1">
       <c r="A199" s="8" t="s">
         <v>141</v>
       </c>
@@ -7502,7 +7500,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="200" spans="1:10" ht="22.5" customHeight="1">
       <c r="A200" s="8" t="s">
         <v>145</v>
       </c>
@@ -7533,7 +7531,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="201" spans="1:10" ht="22.5" customHeight="1">
       <c r="A201" s="8" t="s">
         <v>145</v>
       </c>
@@ -7564,7 +7562,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="202" spans="1:10" ht="22.5" customHeight="1">
       <c r="A202" s="8" t="s">
         <v>145</v>
       </c>
@@ -7595,7 +7593,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="203" spans="1:10" ht="22.5" customHeight="1">
       <c r="A203" s="8" t="s">
         <v>145</v>
       </c>
@@ -7626,7 +7624,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="204" spans="1:10" ht="22.5" customHeight="1">
       <c r="A204" s="8" t="s">
         <v>145</v>
       </c>
@@ -7657,7 +7655,7 @@
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="205" spans="1:10" ht="22.5" customHeight="1">
       <c r="A205" s="8" t="s">
         <v>145</v>
       </c>
@@ -7688,7 +7686,7 @@
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="206" spans="1:10" ht="22.5" customHeight="1">
       <c r="A206" s="8" t="s">
         <v>145</v>
       </c>
@@ -7719,7 +7717,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="207" spans="1:10" ht="22.5" customHeight="1">
       <c r="A207" s="8" t="s">
         <v>145</v>
       </c>
@@ -7750,7 +7748,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="208" spans="1:10" ht="22.5" customHeight="1">
       <c r="A208" s="8" t="s">
         <v>145</v>
       </c>
@@ -7781,7 +7779,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="209" spans="1:10" ht="22.5" customHeight="1">
       <c r="A209" s="8" t="s">
         <v>145</v>
       </c>
@@ -7812,7 +7810,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="210" spans="1:10" ht="22.5" customHeight="1">
       <c r="A210" s="8" t="s">
         <v>145</v>
       </c>
@@ -7843,7 +7841,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="211" spans="1:10" ht="22.5" customHeight="1">
       <c r="A211" s="8" t="s">
         <v>145</v>
       </c>
@@ -7874,7 +7872,7 @@
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="212" spans="1:10" ht="22.5" customHeight="1">
       <c r="A212" s="8" t="s">
         <v>145</v>
       </c>
@@ -7905,7 +7903,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="213" spans="1:10" ht="22.5" customHeight="1">
       <c r="A213" s="8" t="s">
         <v>145</v>
       </c>
@@ -7936,7 +7934,7 @@
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="214" spans="1:10" ht="22.5" customHeight="1">
       <c r="A214" s="8" t="s">
         <v>145</v>
       </c>
@@ -7967,7 +7965,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="215" spans="1:10" ht="22.5" customHeight="1">
       <c r="A215" s="8" t="s">
         <v>145</v>
       </c>
@@ -7998,7 +7996,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="216" spans="1:10" ht="22.5" customHeight="1">
       <c r="A216" s="8" t="s">
         <v>145</v>
       </c>
@@ -8029,7 +8027,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="217" spans="1:10" ht="22.5" customHeight="1">
       <c r="A217" s="8" t="s">
         <v>145</v>
       </c>
@@ -8060,7 +8058,7 @@
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="218" spans="1:10" ht="22.5" customHeight="1">
       <c r="A218" s="8" t="s">
         <v>145</v>
       </c>
@@ -8091,7 +8089,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="219" spans="1:10" ht="22.5" customHeight="1">
       <c r="A219" s="8" t="s">
         <v>145</v>
       </c>
@@ -8122,7 +8120,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="220" spans="1:10" ht="22.5" customHeight="1">
       <c r="A220" s="8" t="s">
         <v>145</v>
       </c>
@@ -8153,7 +8151,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="221" spans="1:10" ht="22.5" customHeight="1">
       <c r="A221" s="8" t="s">
         <v>145</v>
       </c>
@@ -8184,7 +8182,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="222" spans="1:10" ht="22.5" customHeight="1">
       <c r="A222" s="8" t="s">
         <v>145</v>
       </c>
@@ -8215,7 +8213,7 @@
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="223" spans="1:10" ht="22.5" customHeight="1">
       <c r="A223" s="8" t="s">
         <v>145</v>
       </c>
@@ -8246,7 +8244,7 @@
         <v>per Efferevescent tablet</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="224" spans="1:10" ht="22.5" customHeight="1">
       <c r="A224" s="8" t="s">
         <v>145</v>
       </c>
@@ -8277,7 +8275,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="225" spans="1:10" ht="22.5" customHeight="1">
       <c r="A225" s="8" t="s">
         <v>155</v>
       </c>
@@ -8308,7 +8306,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="226" spans="1:10" ht="22.5" customHeight="1">
       <c r="A226" s="8" t="s">
         <v>155</v>
       </c>
@@ -8339,7 +8337,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="227" spans="1:10" ht="22.5" customHeight="1">
       <c r="A227" s="8" t="s">
         <v>155</v>
       </c>
@@ -8370,7 +8368,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="228" spans="1:10" ht="22.5" customHeight="1">
       <c r="A228" s="8" t="s">
         <v>155</v>
       </c>
@@ -8401,7 +8399,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="229" spans="1:10" ht="22.5" customHeight="1">
       <c r="A229" s="8" t="s">
         <v>155</v>
       </c>
@@ -8432,7 +8430,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="230" spans="1:10" ht="22.5" customHeight="1">
       <c r="A230" s="8" t="s">
         <v>155</v>
       </c>
@@ -8463,7 +8461,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="231" spans="1:10" ht="22.5" customHeight="1">
       <c r="A231" s="8" t="s">
         <v>155</v>
       </c>
@@ -8494,7 +8492,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="232" spans="1:10" ht="22.5" customHeight="1">
       <c r="A232" s="8" t="s">
         <v>155</v>
       </c>
@@ -8525,7 +8523,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="233" spans="1:10" ht="22.5" customHeight="1">
       <c r="A233" s="8" t="s">
         <v>155</v>
       </c>
@@ -8556,7 +8554,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="234" spans="1:10" ht="22.5" customHeight="1">
       <c r="A234" s="8" t="s">
         <v>155</v>
       </c>
@@ -8587,7 +8585,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="235" spans="1:10" ht="22.5" customHeight="1">
       <c r="A235" s="8" t="s">
         <v>155</v>
       </c>
@@ -8618,7 +8616,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="236" spans="1:10" ht="22.5" customHeight="1">
       <c r="A236" s="8" t="s">
         <v>23</v>
       </c>
@@ -8649,7 +8647,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="237" spans="1:10" ht="22.5" customHeight="1">
       <c r="A237" s="8" t="s">
         <v>23</v>
       </c>
@@ -8680,7 +8678,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="238" spans="1:10" ht="22.5" customHeight="1">
       <c r="A238" s="8" t="s">
         <v>23</v>
       </c>
@@ -8711,7 +8709,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="239" spans="1:10" ht="22.5" customHeight="1">
       <c r="A239" s="8" t="s">
         <v>23</v>
       </c>
@@ -8742,7 +8740,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="240" spans="1:10" ht="22.5" customHeight="1">
       <c r="A240" s="8" t="s">
         <v>23</v>
       </c>
@@ -8773,7 +8771,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="241" spans="1:10" ht="22.5" customHeight="1">
       <c r="A241" s="8" t="s">
         <v>23</v>
       </c>
@@ -8804,7 +8802,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="242" spans="1:10" ht="22.5" customHeight="1">
       <c r="A242" s="8" t="s">
         <v>23</v>
       </c>
@@ -8835,7 +8833,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="243" spans="1:10" ht="22.5" customHeight="1">
       <c r="A243" s="8" t="s">
         <v>23</v>
       </c>
@@ -8866,7 +8864,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="244" spans="1:10" ht="22.5" customHeight="1">
       <c r="A244" s="8" t="s">
         <v>27</v>
       </c>
@@ -8897,7 +8895,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="245" spans="1:10" ht="22.5" customHeight="1">
       <c r="A245" s="8" t="s">
         <v>27</v>
       </c>
@@ -8928,7 +8926,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="246" spans="1:10" ht="22.5" customHeight="1">
       <c r="A246" s="8" t="s">
         <v>27</v>
       </c>
@@ -8959,7 +8957,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="247" spans="1:10" ht="22.5" customHeight="1">
       <c r="A247" s="8" t="s">
         <v>27</v>
       </c>
@@ -8990,7 +8988,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="248" spans="1:10" ht="22.5" customHeight="1">
       <c r="A248" s="8" t="s">
         <v>27</v>
       </c>
@@ -9021,7 +9019,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="249" spans="1:10" ht="22.5" customHeight="1">
       <c r="A249" s="8" t="s">
         <v>27</v>
       </c>
@@ -9052,7 +9050,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="250" spans="1:10" ht="22.5" customHeight="1">
       <c r="A250" s="8" t="s">
         <v>27</v>
       </c>
@@ -9083,7 +9081,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="251" spans="1:10" ht="22.5" customHeight="1">
       <c r="A251" s="8" t="s">
         <v>27</v>
       </c>
@@ -9114,7 +9112,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="252" spans="1:10" ht="22.5" customHeight="1">
       <c r="A252" s="8" t="s">
         <v>27</v>
       </c>
@@ -9145,7 +9143,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="253" spans="1:10" ht="22.5" customHeight="1">
       <c r="A253" s="8" t="s">
         <v>27</v>
       </c>
@@ -9176,7 +9174,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="254" spans="1:10" ht="22.5" customHeight="1">
       <c r="A254" s="8" t="s">
         <v>27</v>
       </c>
@@ -9207,7 +9205,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="255" spans="1:10" ht="22.5" customHeight="1">
       <c r="A255" s="8" t="s">
         <v>27</v>
       </c>
@@ -9238,7 +9236,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="256" spans="1:10" ht="22.5" customHeight="1">
       <c r="A256" s="8" t="s">
         <v>27</v>
       </c>
@@ -9269,7 +9267,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="257" spans="1:10" ht="22.5" customHeight="1">
       <c r="A257" s="8" t="s">
         <v>27</v>
       </c>
@@ -9300,7 +9298,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="258" spans="1:10" ht="22.5" customHeight="1">
       <c r="A258" s="8" t="s">
         <v>27</v>
       </c>
@@ -9331,7 +9329,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="259" spans="1:10" ht="22.5" customHeight="1">
       <c r="A259" s="8" t="s">
         <v>27</v>
       </c>
@@ -9362,7 +9360,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="260" spans="1:10" ht="22.5" customHeight="1">
       <c r="A260" s="8" t="s">
         <v>27</v>
       </c>
@@ -9393,7 +9391,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="261" spans="1:10" ht="22.5" customHeight="1">
       <c r="A261" s="8" t="s">
         <v>27</v>
       </c>
@@ -9424,7 +9422,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="262" spans="1:10" ht="22.5" customHeight="1">
       <c r="A262" s="8" t="s">
         <v>27</v>
       </c>
@@ -9455,7 +9453,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="263" spans="1:10" ht="22.5" customHeight="1">
       <c r="A263" s="8" t="s">
         <v>27</v>
       </c>
@@ -9486,7 +9484,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="264" spans="1:10" ht="22.5" customHeight="1">
       <c r="A264" s="8" t="s">
         <v>175</v>
       </c>
@@ -9517,7 +9515,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="265" spans="1:10" ht="22.5" customHeight="1">
       <c r="A265" s="8" t="s">
         <v>175</v>
       </c>
@@ -9548,7 +9546,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="266" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="266" spans="1:10" ht="22.5" customHeight="1">
       <c r="A266" s="8" t="s">
         <v>175</v>
       </c>
@@ -9579,7 +9577,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="267" spans="1:10" ht="22.5" customHeight="1">
       <c r="A267" s="8" t="s">
         <v>175</v>
       </c>
@@ -9610,7 +9608,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="268" spans="1:10" ht="22.5" customHeight="1">
       <c r="A268" s="8" t="s">
         <v>175</v>
       </c>
@@ -9641,7 +9639,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="269" spans="1:10" ht="22.5" customHeight="1">
       <c r="A269" s="8" t="s">
         <v>175</v>
       </c>
@@ -9672,7 +9670,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="270" spans="1:10" ht="22.5" customHeight="1">
       <c r="A270" s="8" t="s">
         <v>175</v>
       </c>
@@ -9703,7 +9701,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="271" spans="1:10" ht="22.5" customHeight="1">
       <c r="A271" s="8" t="s">
         <v>35</v>
       </c>
@@ -9734,7 +9732,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="272" spans="1:10" ht="22.5" customHeight="1">
       <c r="A272" s="8" t="s">
         <v>82</v>
       </c>
@@ -9765,7 +9763,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="273" spans="1:10" ht="22.5" customHeight="1">
       <c r="A273" s="8" t="s">
         <v>50</v>
       </c>
@@ -9796,7 +9794,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="274" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="274" spans="1:10" ht="22.5" customHeight="1">
       <c r="A274" s="8" t="s">
         <v>50</v>
       </c>
@@ -9827,7 +9825,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="275" spans="1:10" ht="22.5" customHeight="1">
       <c r="A275" s="8" t="s">
         <v>50</v>
       </c>
@@ -9858,7 +9856,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="276" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="276" spans="1:10" ht="22.5" customHeight="1">
       <c r="A276" s="8" t="s">
         <v>50</v>
       </c>
@@ -9889,7 +9887,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="277" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="277" spans="1:10" ht="22.5" customHeight="1">
       <c r="A277" s="8" t="s">
         <v>50</v>
       </c>
@@ -9920,7 +9918,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="278" spans="1:10" ht="22.5" customHeight="1">
       <c r="A278" s="8" t="s">
         <v>50</v>
       </c>
@@ -9951,7 +9949,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="279" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="279" spans="1:10" ht="22.5" customHeight="1">
       <c r="A279" s="8" t="s">
         <v>50</v>
       </c>
@@ -9982,7 +9980,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="280" spans="1:10" ht="22.5" customHeight="1">
       <c r="A280" s="8" t="s">
         <v>50</v>
       </c>
@@ -10013,7 +10011,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="281" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="281" spans="1:10" ht="22.5" customHeight="1">
       <c r="A281" s="8" t="s">
         <v>50</v>
       </c>
@@ -10044,7 +10042,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="282" spans="1:10" ht="22.5" customHeight="1">
       <c r="A282" s="8" t="s">
         <v>50</v>
       </c>
@@ -10075,7 +10073,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="283" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="283" spans="1:10" ht="22.5" customHeight="1">
       <c r="A283" s="8" t="s">
         <v>50</v>
       </c>
@@ -10106,7 +10104,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="284" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="284" spans="1:10" ht="22.5" customHeight="1">
       <c r="A284" s="8" t="s">
         <v>50</v>
       </c>
@@ -10137,7 +10135,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="285" spans="1:10" ht="22.5" customHeight="1">
       <c r="A285" s="8" t="s">
         <v>50</v>
       </c>
@@ -10168,7 +10166,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="286" spans="1:10" ht="22.5" customHeight="1">
       <c r="A286" s="8" t="s">
         <v>50</v>
       </c>
@@ -10199,7 +10197,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="287" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="287" spans="1:10" ht="22.5" customHeight="1">
       <c r="A287" s="8" t="s">
         <v>66</v>
       </c>
@@ -10230,7 +10228,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="288" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="288" spans="1:10" ht="22.5" customHeight="1">
       <c r="A288" s="8" t="s">
         <v>66</v>
       </c>
@@ -10261,7 +10259,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="289" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="289" spans="1:10" ht="22.5" customHeight="1">
       <c r="A289" s="8" t="s">
         <v>66</v>
       </c>
@@ -10292,7 +10290,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="290" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="290" spans="1:10" ht="22.5" customHeight="1">
       <c r="A290" s="8" t="s">
         <v>66</v>
       </c>
@@ -10323,7 +10321,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="291" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="291" spans="1:10" ht="22.5" customHeight="1">
       <c r="A291" s="8" t="s">
         <v>66</v>
       </c>
@@ -10354,7 +10352,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="292" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="292" spans="1:10" ht="22.5" customHeight="1">
       <c r="A292" s="8" t="s">
         <v>66</v>
       </c>
@@ -10385,7 +10383,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="293" spans="1:10" ht="22.5" customHeight="1">
       <c r="A293" s="8" t="s">
         <v>66</v>
       </c>
@@ -10416,7 +10414,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="294" spans="1:10" ht="22.5" customHeight="1">
       <c r="A294" s="8" t="s">
         <v>66</v>
       </c>
@@ -10447,7 +10445,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="295" spans="1:10" ht="22.5" customHeight="1">
       <c r="A295" s="8" t="s">
         <v>66</v>
       </c>
@@ -10478,7 +10476,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="296" spans="1:10" ht="22.5" customHeight="1">
       <c r="A296" s="8" t="s">
         <v>66</v>
       </c>
@@ -10509,7 +10507,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="297" spans="1:10" ht="22.5" customHeight="1">
       <c r="A297" s="8" t="s">
         <v>66</v>
       </c>
@@ -10540,7 +10538,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="298" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="298" spans="1:10" ht="22.5" customHeight="1">
       <c r="A298" s="8" t="s">
         <v>66</v>
       </c>
@@ -10571,7 +10569,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="299" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="299" spans="1:10" ht="22.5" customHeight="1">
       <c r="A299" s="8" t="s">
         <v>66</v>
       </c>
@@ -10602,7 +10600,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="300" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="300" spans="1:10" ht="22.5" customHeight="1">
       <c r="A300" s="8" t="s">
         <v>66</v>
       </c>
@@ -10633,7 +10631,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="301" spans="1:10" ht="22.5" customHeight="1">
       <c r="A301" s="8" t="s">
         <v>66</v>
       </c>
@@ -10664,7 +10662,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="302" spans="1:10" ht="22.5" customHeight="1">
       <c r="A302" s="8" t="s">
         <v>66</v>
       </c>
@@ -10695,7 +10693,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="303" spans="1:10" ht="22.5" customHeight="1">
       <c r="A303" s="8" t="s">
         <v>66</v>
       </c>
@@ -10726,7 +10724,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="304" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="304" spans="1:10" ht="22.5" customHeight="1">
       <c r="A304" s="8" t="s">
         <v>66</v>
       </c>
@@ -10757,7 +10755,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="305" spans="1:10" ht="22.5" customHeight="1">
       <c r="A305" s="8" t="s">
         <v>66</v>
       </c>
@@ -10788,7 +10786,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="306" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="306" spans="1:10" ht="22.5" customHeight="1">
       <c r="A306" s="8" t="s">
         <v>66</v>
       </c>
@@ -10819,7 +10817,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="307" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="307" spans="1:10" ht="22.5" customHeight="1">
       <c r="A307" s="8" t="s">
         <v>66</v>
       </c>
@@ -10850,7 +10848,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="308" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="308" spans="1:10" ht="22.5" customHeight="1">
       <c r="A308" s="8" t="s">
         <v>66</v>
       </c>
@@ -10881,7 +10879,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="309" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="309" spans="1:10" ht="22.5" customHeight="1">
       <c r="A309" s="8" t="s">
         <v>66</v>
       </c>
@@ -10912,7 +10910,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="310" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="310" spans="1:10" ht="22.5" customHeight="1">
       <c r="A310" s="8" t="s">
         <v>66</v>
       </c>
@@ -10943,7 +10941,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="311" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="311" spans="1:10" ht="22.5" customHeight="1">
       <c r="A311" s="8" t="s">
         <v>66</v>
       </c>
@@ -10974,7 +10972,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="312" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="312" spans="1:10" ht="22.5" customHeight="1">
       <c r="A312" s="8" t="s">
         <v>66</v>
       </c>
@@ -11005,7 +11003,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="313" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="313" spans="1:10" ht="22.5" customHeight="1">
       <c r="A313" s="8" t="s">
         <v>66</v>
       </c>
@@ -11036,7 +11034,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="314" spans="1:10" ht="22.5" customHeight="1">
       <c r="A314" s="8" t="s">
         <v>66</v>
       </c>
@@ -11067,7 +11065,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="315" spans="1:10" ht="22.5" customHeight="1">
       <c r="A315" s="8" t="s">
         <v>66</v>
       </c>
@@ -11098,7 +11096,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="316" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="316" spans="1:10" ht="22.5" customHeight="1">
       <c r="A316" s="8" t="s">
         <v>66</v>
       </c>
@@ -11129,7 +11127,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="317" spans="1:10" ht="22.5" customHeight="1">
       <c r="A317" s="8" t="s">
         <v>66</v>
       </c>
@@ -11160,7 +11158,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="318" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="318" spans="1:10" ht="22.5" customHeight="1">
       <c r="A318" s="8" t="s">
         <v>66</v>
       </c>
@@ -11191,7 +11189,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="319" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="319" spans="1:10" ht="22.5" customHeight="1">
       <c r="A319" s="8" t="s">
         <v>66</v>
       </c>
@@ -11222,7 +11220,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="320" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="320" spans="1:10" ht="22.5" customHeight="1">
       <c r="A320" s="8" t="s">
         <v>66</v>
       </c>
@@ -11253,7 +11251,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="321" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="321" spans="1:10" ht="22.5" customHeight="1">
       <c r="A321" s="8" t="s">
         <v>66</v>
       </c>
@@ -11284,7 +11282,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="322" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="322" spans="1:10" ht="22.5" customHeight="1">
       <c r="A322" s="8" t="s">
         <v>66</v>
       </c>
@@ -11315,7 +11313,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="323" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="323" spans="1:10" ht="22.5" customHeight="1">
       <c r="A323" s="8" t="s">
         <v>66</v>
       </c>
@@ -11346,7 +11344,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="324" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="324" spans="1:10" ht="22.5" customHeight="1">
       <c r="A324" s="8" t="s">
         <v>66</v>
       </c>
@@ -11377,7 +11375,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="325" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="325" spans="1:10" ht="22.5" customHeight="1">
       <c r="A325" s="8" t="s">
         <v>66</v>
       </c>
@@ -11408,7 +11406,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="326" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="326" spans="1:10" ht="22.5" customHeight="1">
       <c r="A326" s="8" t="s">
         <v>69</v>
       </c>
@@ -11439,7 +11437,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="327" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="327" spans="1:10" ht="22.5" customHeight="1">
       <c r="A327" s="8" t="s">
         <v>88</v>
       </c>
@@ -11470,7 +11468,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="328" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="328" spans="1:10" ht="22.5" customHeight="1">
       <c r="A328" s="8" t="s">
         <v>88</v>
       </c>
@@ -11501,7 +11499,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="329" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="329" spans="1:10" ht="22.5" customHeight="1">
       <c r="A329" s="8" t="s">
         <v>88</v>
       </c>
@@ -11532,7 +11530,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="330" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="330" spans="1:10" ht="22.5" customHeight="1">
       <c r="A330" s="8" t="s">
         <v>88</v>
       </c>
@@ -11563,7 +11561,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="331" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="331" spans="1:10" ht="22.5" customHeight="1">
       <c r="A331" s="8" t="s">
         <v>88</v>
       </c>
@@ -11594,7 +11592,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="332" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="332" spans="1:10" ht="22.5" customHeight="1">
       <c r="A332" s="8" t="s">
         <v>88</v>
       </c>
@@ -11625,7 +11623,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="333" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="333" spans="1:10" ht="22.5" customHeight="1">
       <c r="A333" s="8" t="s">
         <v>88</v>
       </c>
@@ -11656,7 +11654,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="334" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="334" spans="1:10" ht="22.5" customHeight="1">
       <c r="A334" s="8" t="s">
         <v>88</v>
       </c>
@@ -11687,7 +11685,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="335" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="335" spans="1:10" ht="22.5" customHeight="1">
       <c r="A335" s="8" t="s">
         <v>88</v>
       </c>
@@ -11718,7 +11716,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="336" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="336" spans="1:10" ht="22.5" customHeight="1">
       <c r="A336" s="8" t="s">
         <v>88</v>
       </c>
@@ -11749,7 +11747,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="337" spans="1:10" ht="22.5" customHeight="1">
       <c r="A337" s="8" t="s">
         <v>71</v>
       </c>
@@ -11780,7 +11778,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="338" spans="1:10" ht="22.5" customHeight="1">
       <c r="A338" s="8" t="s">
         <v>71</v>
       </c>
@@ -11811,7 +11809,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="339" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="339" spans="1:10" ht="22.5" customHeight="1">
       <c r="A339" s="8" t="s">
         <v>71</v>
       </c>
@@ -11842,7 +11840,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="340" spans="1:10" ht="22.5" customHeight="1">
       <c r="A340" s="8" t="s">
         <v>71</v>
       </c>
@@ -11873,7 +11871,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="341" spans="1:10" ht="22.5" customHeight="1">
       <c r="A341" s="8" t="s">
         <v>71</v>
       </c>
@@ -11904,7 +11902,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="342" spans="1:10" ht="22.5" customHeight="1">
       <c r="A342" s="8" t="s">
         <v>71</v>
       </c>
@@ -11935,7 +11933,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="343" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="343" spans="1:10" ht="22.5" customHeight="1">
       <c r="A343" s="8" t="s">
         <v>71</v>
       </c>
@@ -11966,7 +11964,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="344" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="344" spans="1:10" ht="22.5" customHeight="1">
       <c r="A344" s="8" t="s">
         <v>71</v>
       </c>
@@ -11997,7 +11995,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="345" spans="1:10" ht="22.5" customHeight="1">
       <c r="A345" s="8" t="s">
         <v>71</v>
       </c>
@@ -12028,7 +12026,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="346" spans="1:10" ht="22.5" customHeight="1">
       <c r="A346" s="8" t="s">
         <v>71</v>
       </c>
@@ -12059,7 +12057,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="347" spans="1:10" ht="22.5" customHeight="1">
       <c r="A347" s="8" t="s">
         <v>71</v>
       </c>
@@ -12090,7 +12088,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="348" spans="1:10" ht="22.5" customHeight="1">
       <c r="A348" s="8" t="s">
         <v>71</v>
       </c>
@@ -12121,7 +12119,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="349" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="349" spans="1:10" ht="22.5" customHeight="1">
       <c r="A349" s="8" t="s">
         <v>71</v>
       </c>
@@ -12152,7 +12150,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="350" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="350" spans="1:10" ht="22.5" customHeight="1">
       <c r="A350" s="8" t="s">
         <v>71</v>
       </c>
@@ -12183,7 +12181,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="351" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="351" spans="1:10" ht="22.5" customHeight="1">
       <c r="A351" s="8" t="s">
         <v>71</v>
       </c>
@@ -12214,7 +12212,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="352" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="352" spans="1:10" ht="22.5" customHeight="1">
       <c r="A352" s="8" t="s">
         <v>71</v>
       </c>
@@ -12245,7 +12243,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="353" spans="1:10" ht="22.5" customHeight="1">
       <c r="A353" s="8" t="s">
         <v>71</v>
       </c>
@@ -12276,7 +12274,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="354" spans="1:10" ht="22.5" customHeight="1">
       <c r="A354" s="8" t="s">
         <v>71</v>
       </c>
@@ -12307,7 +12305,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="355" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="355" spans="1:10" ht="22.5" customHeight="1">
       <c r="A355" s="8" t="s">
         <v>71</v>
       </c>
@@ -12338,7 +12336,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="356" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="356" spans="1:10" ht="22.5" customHeight="1">
       <c r="A356" s="8" t="s">
         <v>71</v>
       </c>
@@ -12369,7 +12367,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="357" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="357" spans="1:10" ht="22.5" customHeight="1">
       <c r="A357" s="8" t="s">
         <v>71</v>
       </c>
@@ -12400,7 +12398,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="358" spans="1:10" ht="22.5" customHeight="1">
       <c r="A358" s="8" t="s">
         <v>71</v>
       </c>
@@ -12431,7 +12429,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="359" spans="1:10" ht="22.5" customHeight="1">
       <c r="A359" s="8" t="s">
         <v>71</v>
       </c>
@@ -12462,7 +12460,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="360" spans="1:10" ht="22.5" customHeight="1">
       <c r="A360" s="8" t="s">
         <v>71</v>
       </c>
@@ -12493,7 +12491,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="361" spans="1:10" ht="22.5" customHeight="1">
       <c r="A361" s="8" t="s">
         <v>71</v>
       </c>
@@ -12524,7 +12522,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="362" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="362" spans="1:10" ht="22.5" customHeight="1">
       <c r="A362" s="8" t="s">
         <v>71</v>
       </c>
@@ -12555,7 +12553,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="363" spans="1:10" ht="22.5" customHeight="1">
       <c r="A363" s="8" t="s">
         <v>71</v>
       </c>
@@ -12586,7 +12584,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="364" spans="1:10" ht="22.5" customHeight="1">
       <c r="A364" s="8" t="s">
         <v>71</v>
       </c>
@@ -12617,7 +12615,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="365" spans="1:10" ht="22.5" customHeight="1">
       <c r="A365" s="8" t="s">
         <v>71</v>
       </c>
@@ -12648,7 +12646,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="366" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="366" spans="1:10" ht="22.5" customHeight="1">
       <c r="A366" s="8" t="s">
         <v>71</v>
       </c>
@@ -12679,7 +12677,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="367" spans="1:10" ht="22.5" customHeight="1">
       <c r="A367" s="8" t="s">
         <v>71</v>
       </c>
@@ -12710,7 +12708,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="368" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="368" spans="1:10" ht="22.5" customHeight="1">
       <c r="A368" s="8" t="s">
         <v>71</v>
       </c>
@@ -12741,7 +12739,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="369" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="369" spans="1:10" ht="22.5" customHeight="1">
       <c r="A369" s="8" t="s">
         <v>71</v>
       </c>
@@ -12772,7 +12770,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="370" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="370" spans="1:10" ht="22.5" customHeight="1">
       <c r="A370" s="8" t="s">
         <v>71</v>
       </c>
@@ -12803,7 +12801,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="371" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="371" spans="1:10" ht="22.5" customHeight="1">
       <c r="A371" s="8" t="s">
         <v>71</v>
       </c>
@@ -12834,7 +12832,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="372" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="372" spans="1:10" ht="22.5" customHeight="1">
       <c r="A372" s="8" t="s">
         <v>71</v>
       </c>
@@ -12865,7 +12863,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="373" spans="1:10" ht="22.5" customHeight="1">
       <c r="A373" s="8" t="s">
         <v>71</v>
       </c>
@@ -12896,7 +12894,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="374" spans="1:10" ht="22.5" customHeight="1">
       <c r="A374" s="8" t="s">
         <v>71</v>
       </c>
@@ -12927,7 +12925,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="375" spans="1:10" ht="22.5" customHeight="1">
       <c r="A375" s="8" t="s">
         <v>71</v>
       </c>
@@ -12958,7 +12956,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="376" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="376" spans="1:10" ht="22.5" customHeight="1">
       <c r="A376" s="8" t="s">
         <v>71</v>
       </c>
@@ -12989,7 +12987,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="377" spans="1:10" ht="22.5" customHeight="1">
       <c r="A377" s="8" t="s">
         <v>71</v>
       </c>
@@ -13020,7 +13018,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="378" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="378" spans="1:10" ht="22.5" customHeight="1">
       <c r="A378" s="8" t="s">
         <v>71</v>
       </c>
@@ -13051,7 +13049,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="379" spans="1:10" ht="22.5" customHeight="1">
       <c r="A379" s="8" t="s">
         <v>71</v>
       </c>
@@ -13082,7 +13080,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="380" spans="1:10" ht="22.5" customHeight="1">
       <c r="A380" s="8" t="s">
         <v>71</v>
       </c>
@@ -13113,7 +13111,7 @@
         <v>per Tablet</v>
       </c>
     </row>
-    <row r="381" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="381" spans="1:10" ht="22.5" customHeight="1">
       <c r="A381" s="3"/>
       <c r="B381" s="4"/>
       <c r="C381" s="3"/>
@@ -13124,7 +13122,7 @@
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
     </row>
-    <row r="382" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="382" spans="1:10" ht="22.5" customHeight="1">
       <c r="A382" s="3"/>
       <c r="B382" s="4"/>
       <c r="C382" s="3"/>
@@ -13135,7 +13133,7 @@
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
     </row>
-    <row r="383" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="383" spans="1:10" ht="22.5" customHeight="1">
       <c r="A383" s="3"/>
       <c r="B383" s="4"/>
       <c r="C383" s="3"/>
@@ -13146,7 +13144,7 @@
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
     </row>
-    <row r="384" spans="1:10" ht="22.5" hidden="1" customHeight="1">
+    <row r="384" spans="1:10" ht="22.5" customHeight="1">
       <c r="A384" s="3"/>
       <c r="B384" s="4"/>
       <c r="C384" s="3"/>
@@ -13157,7 +13155,7 @@
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
     </row>
-    <row r="385" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="385" spans="1:9" ht="22.5" customHeight="1">
       <c r="A385" s="3"/>
       <c r="B385" s="4"/>
       <c r="C385" s="3"/>
@@ -13168,7 +13166,7 @@
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
     </row>
-    <row r="386" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="386" spans="1:9" ht="22.5" customHeight="1">
       <c r="A386" s="3"/>
       <c r="B386" s="4"/>
       <c r="C386" s="3"/>
@@ -13179,7 +13177,7 @@
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
     </row>
-    <row r="387" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="387" spans="1:9" ht="22.5" customHeight="1">
       <c r="A387" s="3"/>
       <c r="B387" s="4"/>
       <c r="C387" s="3"/>
@@ -13190,7 +13188,7 @@
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
     </row>
-    <row r="388" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="388" spans="1:9" ht="22.5" customHeight="1">
       <c r="A388" s="3"/>
       <c r="B388" s="4"/>
       <c r="C388" s="3"/>
@@ -13201,7 +13199,7 @@
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
     </row>
-    <row r="389" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="389" spans="1:9" ht="22.5" customHeight="1">
       <c r="A389" s="3"/>
       <c r="B389" s="4"/>
       <c r="C389" s="3"/>
@@ -13212,7 +13210,7 @@
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
     </row>
-    <row r="390" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="390" spans="1:9" ht="22.5" customHeight="1">
       <c r="A390" s="3"/>
       <c r="B390" s="4"/>
       <c r="C390" s="3"/>
@@ -13223,7 +13221,7 @@
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
     </row>
-    <row r="391" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="391" spans="1:9" ht="22.5" customHeight="1">
       <c r="A391" s="3"/>
       <c r="B391" s="4"/>
       <c r="C391" s="3"/>
@@ -13234,7 +13232,7 @@
       <c r="H391" s="4"/>
       <c r="I391" s="4"/>
     </row>
-    <row r="392" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="392" spans="1:9" ht="22.5" customHeight="1">
       <c r="A392" s="3"/>
       <c r="B392" s="4"/>
       <c r="C392" s="3"/>
@@ -13245,7 +13243,7 @@
       <c r="H392" s="4"/>
       <c r="I392" s="4"/>
     </row>
-    <row r="393" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="393" spans="1:9" ht="22.5" customHeight="1">
       <c r="A393" s="3"/>
       <c r="B393" s="4"/>
       <c r="C393" s="3"/>
@@ -13256,7 +13254,7 @@
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
     </row>
-    <row r="394" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="394" spans="1:9" ht="22.5" customHeight="1">
       <c r="A394" s="3"/>
       <c r="B394" s="4"/>
       <c r="C394" s="3"/>
@@ -13267,7 +13265,7 @@
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
     </row>
-    <row r="395" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="395" spans="1:9" ht="22.5" customHeight="1">
       <c r="A395" s="3"/>
       <c r="B395" s="4"/>
       <c r="C395" s="3"/>
@@ -13278,7 +13276,7 @@
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
     </row>
-    <row r="396" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="396" spans="1:9" ht="22.5" customHeight="1">
       <c r="A396" s="3"/>
       <c r="B396" s="4"/>
       <c r="C396" s="3"/>
@@ -13289,7 +13287,7 @@
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
     </row>
-    <row r="397" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="397" spans="1:9" ht="22.5" customHeight="1">
       <c r="A397" s="3"/>
       <c r="B397" s="4"/>
       <c r="C397" s="3"/>
@@ -13300,7 +13298,7 @@
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
     </row>
-    <row r="398" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="398" spans="1:9" ht="22.5" customHeight="1">
       <c r="A398" s="3"/>
       <c r="B398" s="4"/>
       <c r="C398" s="3"/>
@@ -13311,7 +13309,7 @@
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
     </row>
-    <row r="399" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="399" spans="1:9" ht="22.5" customHeight="1">
       <c r="A399" s="3"/>
       <c r="B399" s="4"/>
       <c r="C399" s="3"/>
@@ -13322,7 +13320,7 @@
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
     </row>
-    <row r="400" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="400" spans="1:9" ht="22.5" customHeight="1">
       <c r="A400" s="3"/>
       <c r="B400" s="4"/>
       <c r="C400" s="3"/>
@@ -13333,7 +13331,7 @@
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
     </row>
-    <row r="401" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="401" spans="1:9" ht="22.5" customHeight="1">
       <c r="A401" s="3"/>
       <c r="B401" s="4"/>
       <c r="C401" s="3"/>
@@ -13344,7 +13342,7 @@
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
     </row>
-    <row r="402" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="402" spans="1:9" ht="22.5" customHeight="1">
       <c r="A402" s="3"/>
       <c r="B402" s="4"/>
       <c r="C402" s="3"/>
@@ -13355,7 +13353,7 @@
       <c r="H402" s="4"/>
       <c r="I402" s="4"/>
     </row>
-    <row r="403" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="403" spans="1:9" ht="22.5" customHeight="1">
       <c r="A403" s="3"/>
       <c r="B403" s="4"/>
       <c r="C403" s="3"/>
@@ -13366,7 +13364,7 @@
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
     </row>
-    <row r="404" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="404" spans="1:9" ht="22.5" customHeight="1">
       <c r="A404" s="3"/>
       <c r="B404" s="4"/>
       <c r="C404" s="3"/>
@@ -13377,7 +13375,7 @@
       <c r="H404" s="4"/>
       <c r="I404" s="4"/>
     </row>
-    <row r="405" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="405" spans="1:9" ht="22.5" customHeight="1">
       <c r="A405" s="3"/>
       <c r="B405" s="4"/>
       <c r="C405" s="3"/>
@@ -13388,7 +13386,7 @@
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
     </row>
-    <row r="406" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="406" spans="1:9" ht="22.5" customHeight="1">
       <c r="A406" s="3"/>
       <c r="B406" s="4"/>
       <c r="C406" s="3"/>
@@ -13399,7 +13397,7 @@
       <c r="H406" s="4"/>
       <c r="I406" s="4"/>
     </row>
-    <row r="407" spans="1:9" ht="22.5" hidden="1" customHeight="1">
+    <row r="407" spans="1:9" ht="22.5" customHeight="1">
       <c r="A407" s="3"/>
       <c r="B407" s="4"/>
       <c r="C407" s="3"/>
@@ -13411,18 +13409,6 @@
       <c r="I407" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B407" xr:uid="{537DEBE9-B305-49C6-BA8B-E5C9DA8CC8BE}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Buprenorphine"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Tablet"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A200:J224">
     <sortCondition ref="C2:C407"/>
   </sortState>
